--- a/data/sports/npb/research.xlsx
+++ b/data/sports/npb/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ208" headerRowCount="1">
-  <autoFilter ref="A1:DQ208"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ209" headerRowCount="1">
+  <autoFilter ref="A1:DQ209"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$208)</f>
+        <f>COUNTA('Picks'!$A$2:$A$209)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$208,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$209,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$208,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$209,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$208,"settled",'Picks'!$V$2:$V$208,"win")+COUNTIFS('Picks'!$U$2:$U$208,"settled",'Picks'!$V$2:$V$208,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$209,"settled",'Picks'!$V$2:$V$209,"win")+COUNTIFS('Picks'!$U$2:$U$209,"settled",'Picks'!$V$2:$V$209,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$208,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$209,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$208,"&gt;0",'Picks'!$V$2:$V$208,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$208,"&gt;0",'Picks'!$V$2:$V$208,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$209,"&gt;0",'Picks'!$V$2:$V$209,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$209,"&gt;0",'Picks'!$V$2:$V$209,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$208,"&gt;0",'Picks'!$V$2:$V$208,"win")/(COUNTIFS('Picks'!$BX$2:$BX$208,"&gt;0",'Picks'!$V$2:$V$208,"win")+COUNTIFS('Picks'!$BX$2:$BX$208,"&gt;0",'Picks'!$V$2:$V$208,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$209,"&gt;0",'Picks'!$V$2:$V$209,"win")/(COUNTIFS('Picks'!$BX$2:$BX$209,"&gt;0",'Picks'!$V$2:$V$209,"win")+COUNTIFS('Picks'!$BX$2:$BX$209,"&gt;0",'Picks'!$V$2:$V$209,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$208)/SUM('Picks'!$BX$2:$BX$208),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$209)/SUM('Picks'!$BX$2:$BX$209),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$208)</f>
+        <f>SUM('Picks'!$BY$2:$BY$209)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$208,"&lt;&gt;",'Picks'!$AB$2:$AB$208),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$209,"&lt;&gt;",'Picks'!$AB$2:$AB$209),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$208,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$208,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$209,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$209,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$208,'Picks'!$AM$2:$AM$208,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$209,'Picks'!$AM$2:$AM$209,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$208,$A14,'Picks'!$U$2:$U$208,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$209,$A14,'Picks'!$U$2:$U$209,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$208,$A14,'Picks'!$U$2:$U$208,"settled",'Picks'!$V$2:$V$208,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$209,$A14,'Picks'!$U$2:$U$209,"settled",'Picks'!$V$2:$V$209,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$208,$A14,'Picks'!$U$2:$U$208,"settled",'Picks'!$V$2:$V$208,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$209,$A14,'Picks'!$U$2:$U$209,"settled",'Picks'!$V$2:$V$209,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$208,'Picks'!$H$2:$H$208,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$209,'Picks'!$H$2:$H$209,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$208,'Picks'!$H$2:$H$208,$A14,'Picks'!$U$2:$U$208,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$209,'Picks'!$H$2:$H$209,$A14,'Picks'!$U$2:$U$209,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$208,$A15,'Picks'!$U$2:$U$208,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$209,$A15,'Picks'!$U$2:$U$209,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$208,$A15,'Picks'!$U$2:$U$208,"settled",'Picks'!$V$2:$V$208,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$209,$A15,'Picks'!$U$2:$U$209,"settled",'Picks'!$V$2:$V$209,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$208,$A15,'Picks'!$U$2:$U$208,"settled",'Picks'!$V$2:$V$208,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$209,$A15,'Picks'!$U$2:$U$209,"settled",'Picks'!$V$2:$V$209,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$208,'Picks'!$H$2:$H$208,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$209,'Picks'!$H$2:$H$209,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$208,'Picks'!$H$2:$H$208,$A15,'Picks'!$U$2:$U$208,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$209,'Picks'!$H$2:$H$209,$A15,'Picks'!$U$2:$U$209,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$208,$A16,'Picks'!$U$2:$U$208,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$209,$A16,'Picks'!$U$2:$U$209,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$208,$A16,'Picks'!$U$2:$U$208,"settled",'Picks'!$V$2:$V$208,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$209,$A16,'Picks'!$U$2:$U$209,"settled",'Picks'!$V$2:$V$209,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$208,$A16,'Picks'!$U$2:$U$208,"settled",'Picks'!$V$2:$V$208,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$209,$A16,'Picks'!$U$2:$U$209,"settled",'Picks'!$V$2:$V$209,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$208,'Picks'!$H$2:$H$208,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$209,'Picks'!$H$2:$H$209,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$208,'Picks'!$H$2:$H$208,$A16,'Picks'!$U$2:$U$208,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$209,'Picks'!$H$2:$H$209,$A16,'Picks'!$U$2:$U$209,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ208"/>
+  <dimension ref="A1:DQ209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -42433,18 +42433,28 @@
       </c>
       <c r="U131" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V131" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V131" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W131" s="26" t="n"/>
       <c r="X131" s="26" t="n"/>
       <c r="Y131" s="25" t="n"/>
       <c r="Z131" s="26" t="n"/>
       <c r="AA131" s="28" t="n"/>
       <c r="AB131" s="28" t="n"/>
-      <c r="AC131" s="30" t="n"/>
-      <c r="AD131" s="24" t="n"/>
+      <c r="AC131" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD131" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:59:32.469557Z</t>
+        </is>
+      </c>
       <c r="AE131" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.4700 (market_slug=aec-npb-tys-cdh-2026-09-06). Tie probability=0.0355.</t>
@@ -42593,7 +42603,11 @@
       <c r="BT131" s="28" t="n"/>
       <c r="BU131" s="25" t="n"/>
       <c r="BV131" s="29" t="n"/>
-      <c r="BW131" s="24" t="n"/>
+      <c r="BW131" s="24" t="inlineStr">
+        <is>
+          <t>NPB game scheduled on 2026-09-06 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX131" s="30" t="n"/>
       <c r="BY131" s="27" t="n"/>
       <c r="BZ131" s="24" t="n"/>
@@ -44656,18 +44670,28 @@
       </c>
       <c r="U138" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V138" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V138" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W138" s="26" t="n"/>
       <c r="X138" s="26" t="n"/>
       <c r="Y138" s="25" t="n"/>
       <c r="Z138" s="26" t="n"/>
       <c r="AA138" s="28" t="n"/>
       <c r="AB138" s="28" t="n"/>
-      <c r="AC138" s="30" t="n"/>
-      <c r="AD138" s="24" t="n"/>
+      <c r="AC138" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD138" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:59:35.834543Z</t>
+        </is>
+      </c>
       <c r="AE138" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6700 (market_slug=aec-npb-hta-hci-2026-09-08). Tie probability=0.0201.</t>
@@ -44816,7 +44840,11 @@
       <c r="BT138" s="28" t="n"/>
       <c r="BU138" s="25" t="n"/>
       <c r="BV138" s="29" t="n"/>
-      <c r="BW138" s="24" t="n"/>
+      <c r="BW138" s="24" t="inlineStr">
+        <is>
+          <t>NPB game scheduled on 2026-09-08 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX138" s="30" t="n"/>
       <c r="BY138" s="27" t="n"/>
       <c r="BZ138" s="24" t="n"/>
@@ -48175,18 +48203,28 @@
       </c>
       <c r="U149" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V149" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V149" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W149" s="26" t="n"/>
       <c r="X149" s="26" t="n"/>
       <c r="Y149" s="25" t="n"/>
       <c r="Z149" s="26" t="n"/>
       <c r="AA149" s="28" t="n"/>
       <c r="AB149" s="28" t="n"/>
-      <c r="AC149" s="30" t="n"/>
-      <c r="AD149" s="24" t="n"/>
+      <c r="AC149" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD149" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:59:38.976537Z</t>
+        </is>
+      </c>
       <c r="AE149" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-npb-hta-hci-2026-09-10). Tie probability=0.0213.</t>
@@ -48335,7 +48373,11 @@
       <c r="BT149" s="28" t="n"/>
       <c r="BU149" s="25" t="n"/>
       <c r="BV149" s="29" t="n"/>
-      <c r="BW149" s="24" t="n"/>
+      <c r="BW149" s="24" t="inlineStr">
+        <is>
+          <t>NPB game scheduled on 2026-09-10 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX149" s="30" t="n"/>
       <c r="BY149" s="27" t="n"/>
       <c r="BZ149" s="24" t="n"/>
@@ -54886,18 +54928,28 @@
       </c>
       <c r="U170" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V170" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V170" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W170" s="26" t="n"/>
       <c r="X170" s="26" t="n"/>
       <c r="Y170" s="25" t="n"/>
       <c r="Z170" s="26" t="n"/>
       <c r="AA170" s="28" t="n"/>
       <c r="AB170" s="28" t="n"/>
-      <c r="AC170" s="30" t="n"/>
-      <c r="AD170" s="24" t="n"/>
+      <c r="AC170" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD170" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:59:42.214913Z</t>
+        </is>
+      </c>
       <c r="AE170" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-npb-clm-ssl-2026-09-20). Tie probability=0.0240.</t>
@@ -55046,7 +55098,11 @@
       <c r="BT170" s="28" t="n"/>
       <c r="BU170" s="25" t="n"/>
       <c r="BV170" s="29" t="n"/>
-      <c r="BW170" s="24" t="n"/>
+      <c r="BW170" s="24" t="inlineStr">
+        <is>
+          <t>NPB game scheduled on 2026-09-20 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX170" s="30" t="n"/>
       <c r="BY170" s="27" t="n"/>
       <c r="BZ170" s="24" t="n"/>
@@ -55187,18 +55243,28 @@
       </c>
       <c r="U171" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V171" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V171" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W171" s="26" t="n"/>
       <c r="X171" s="26" t="n"/>
       <c r="Y171" s="25" t="n"/>
       <c r="Z171" s="26" t="n"/>
       <c r="AA171" s="28" t="n"/>
       <c r="AB171" s="28" t="n"/>
-      <c r="AC171" s="30" t="n"/>
-      <c r="AD171" s="24" t="n"/>
+      <c r="AC171" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD171" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:59:45.404797Z</t>
+        </is>
+      </c>
       <c r="AE171" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-npb-trge-fsh-2026-09-21). Tie probability=0.0285.</t>
@@ -55347,7 +55413,11 @@
       <c r="BT171" s="28" t="n"/>
       <c r="BU171" s="25" t="n"/>
       <c r="BV171" s="29" t="n"/>
-      <c r="BW171" s="24" t="n"/>
+      <c r="BW171" s="24" t="inlineStr">
+        <is>
+          <t>NPB game scheduled on 2026-09-21 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX171" s="30" t="n"/>
       <c r="BY171" s="27" t="n"/>
       <c r="BZ171" s="24" t="n"/>
@@ -56433,18 +56503,28 @@
       </c>
       <c r="U175" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V175" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V175" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W175" s="26" t="n"/>
       <c r="X175" s="26" t="n"/>
       <c r="Y175" s="25" t="n"/>
       <c r="Z175" s="26" t="n"/>
       <c r="AA175" s="28" t="n"/>
       <c r="AB175" s="28" t="n"/>
-      <c r="AC175" s="30" t="n"/>
-      <c r="AD175" s="24" t="n"/>
+      <c r="AC175" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD175" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:59:48.518732Z</t>
+        </is>
+      </c>
       <c r="AE175" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-npb-clm-ssl-2026-09-21). Tie probability=0.0349.</t>
@@ -56593,7 +56673,11 @@
       <c r="BT175" s="28" t="n"/>
       <c r="BU175" s="25" t="n"/>
       <c r="BV175" s="29" t="n"/>
-      <c r="BW175" s="24" t="n"/>
+      <c r="BW175" s="24" t="inlineStr">
+        <is>
+          <t>NPB game scheduled on 2026-09-21 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX175" s="30" t="n"/>
       <c r="BY175" s="27" t="n"/>
       <c r="BZ175" s="24" t="n"/>
@@ -63074,18 +63158,38 @@
       </c>
       <c r="U196" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V196" s="24" t="n"/>
-      <c r="W196" s="26" t="n"/>
-      <c r="X196" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V196" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W196" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X196" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y196" s="25" t="n"/>
-      <c r="Z196" s="26" t="n"/>
-      <c r="AA196" s="28" t="n"/>
-      <c r="AB196" s="28" t="n"/>
-      <c r="AC196" s="30" t="n"/>
-      <c r="AD196" s="24" t="n"/>
+      <c r="Z196" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA196" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB196" s="28" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AC196" s="30" t="n">
+        <v>-0.2059</v>
+      </c>
+      <c r="AD196" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:12.154946Z</t>
+        </is>
+      </c>
       <c r="AE196" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6300 (market_slug=aec-npb-hta-ygo-2026-10-01). Tie probability=0.0238.</t>
@@ -63228,8 +63332,12 @@
       <c r="BN196" s="28" t="n"/>
       <c r="BO196" s="28" t="n"/>
       <c r="BP196" s="25" t="n"/>
-      <c r="BQ196" s="27" t="n"/>
-      <c r="BR196" s="28" t="n"/>
+      <c r="BQ196" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR196" s="28" t="n">
+        <v>0.63</v>
+      </c>
       <c r="BS196" s="28" t="n"/>
       <c r="BT196" s="28" t="n"/>
       <c r="BU196" s="25" t="n"/>
@@ -63375,18 +63483,38 @@
       </c>
       <c r="U197" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V197" s="24" t="n"/>
-      <c r="W197" s="26" t="n"/>
-      <c r="X197" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V197" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W197" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X197" s="26" t="n">
+        <v>5</v>
+      </c>
       <c r="Y197" s="25" t="n"/>
-      <c r="Z197" s="26" t="n"/>
-      <c r="AA197" s="28" t="n"/>
-      <c r="AB197" s="28" t="n"/>
-      <c r="AC197" s="30" t="n"/>
-      <c r="AD197" s="24" t="n"/>
+      <c r="Z197" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA197" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB197" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC197" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD197" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:13.692835Z</t>
+        </is>
+      </c>
       <c r="AE197" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5000 (market_slug=aec-npb-hci-cdh-2026-10-01). Tie probability=0.0238.</t>
@@ -63529,8 +63657,12 @@
       <c r="BN197" s="28" t="n"/>
       <c r="BO197" s="28" t="n"/>
       <c r="BP197" s="25" t="n"/>
-      <c r="BQ197" s="27" t="n"/>
-      <c r="BR197" s="28" t="n"/>
+      <c r="BQ197" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR197" s="28" t="n">
+        <v>0.5</v>
+      </c>
       <c r="BS197" s="28" t="n"/>
       <c r="BT197" s="28" t="n"/>
       <c r="BU197" s="25" t="n"/>
@@ -63676,18 +63808,32 @@
       </c>
       <c r="U198" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V198" s="24" t="n"/>
-      <c r="W198" s="26" t="n"/>
-      <c r="X198" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V198" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W198" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X198" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="Y198" s="25" t="n"/>
       <c r="Z198" s="26" t="n"/>
       <c r="AA198" s="28" t="n"/>
       <c r="AB198" s="28" t="n"/>
-      <c r="AC198" s="30" t="n"/>
-      <c r="AD198" s="24" t="n"/>
+      <c r="AC198" s="30" t="n">
+        <v>0.4926</v>
+      </c>
+      <c r="AD198" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:15.169021Z</t>
+        </is>
+      </c>
       <c r="AE198" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6700 (market_slug=aec-npb-clm-fsh-2026-10-02). Tie probability=0.0238.</t>
@@ -63977,18 +64123,32 @@
       </c>
       <c r="U199" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V199" s="24" t="n"/>
-      <c r="W199" s="26" t="n"/>
-      <c r="X199" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V199" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W199" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X199" s="26" t="n">
+        <v>5</v>
+      </c>
       <c r="Y199" s="25" t="n"/>
       <c r="Z199" s="26" t="n"/>
       <c r="AA199" s="28" t="n"/>
       <c r="AB199" s="28" t="n"/>
-      <c r="AC199" s="30" t="n"/>
-      <c r="AD199" s="24" t="n"/>
+      <c r="AC199" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD199" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:16.744797Z</t>
+        </is>
+      </c>
       <c r="AE199" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5600 (market_slug=aec-npb-tys-ygo-2026-10-02). Tie probability=0.0238.</t>
@@ -64001,7 +64161,7 @@
       </c>
       <c r="AG199" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH199" s="24" t="n"/>
@@ -64278,18 +64438,32 @@
       </c>
       <c r="U200" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V200" s="24" t="n"/>
-      <c r="W200" s="26" t="n"/>
-      <c r="X200" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V200" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W200" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X200" s="26" t="n">
+        <v>6</v>
+      </c>
       <c r="Y200" s="25" t="n"/>
       <c r="Z200" s="26" t="n"/>
       <c r="AA200" s="28" t="n"/>
       <c r="AB200" s="28" t="n"/>
-      <c r="AC200" s="30" t="n"/>
-      <c r="AD200" s="24" t="n"/>
+      <c r="AC200" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD200" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:18.316422Z</t>
+        </is>
+      </c>
       <c r="AE200" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6400 (market_slug=aec-npb-hci-hta-2026-10-03). Tie probability=0.0238.</t>
@@ -64302,7 +64476,7 @@
       </c>
       <c r="AG200" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH200" s="24" t="n"/>
@@ -64579,18 +64753,32 @@
       </c>
       <c r="U201" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V201" s="24" t="n"/>
-      <c r="W201" s="26" t="n"/>
-      <c r="X201" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V201" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W201" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X201" s="26" t="n">
+        <v>6</v>
+      </c>
       <c r="Y201" s="25" t="n"/>
       <c r="Z201" s="26" t="n"/>
       <c r="AA201" s="28" t="n"/>
       <c r="AB201" s="28" t="n"/>
-      <c r="AC201" s="30" t="n"/>
-      <c r="AD201" s="24" t="n"/>
+      <c r="AC201" s="30" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+      <c r="AD201" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:19.870751Z</t>
+        </is>
+      </c>
       <c r="AE201" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5200 (market_slug=aec-npb-trge-obr-2026-10-03). Tie probability=0.0238.</t>
@@ -64880,18 +65068,32 @@
       </c>
       <c r="U202" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V202" s="24" t="n"/>
-      <c r="W202" s="26" t="n"/>
-      <c r="X202" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V202" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W202" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X202" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y202" s="25" t="n"/>
       <c r="Z202" s="26" t="n"/>
       <c r="AA202" s="28" t="n"/>
       <c r="AB202" s="28" t="n"/>
-      <c r="AC202" s="30" t="n"/>
-      <c r="AD202" s="24" t="n"/>
+      <c r="AC202" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD202" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:21.396595Z</t>
+        </is>
+      </c>
       <c r="AE202" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.4600 (market_slug=aec-npb-tys-cdh-2026-10-03). Tie probability=0.0238.</t>
@@ -64904,7 +65106,7 @@
       </c>
       <c r="AG202" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH202" s="24" t="n"/>
@@ -65181,18 +65383,32 @@
       </c>
       <c r="U203" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V203" s="24" t="n"/>
-      <c r="W203" s="26" t="n"/>
-      <c r="X203" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V203" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W203" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="X203" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y203" s="25" t="n"/>
       <c r="Z203" s="26" t="n"/>
       <c r="AA203" s="28" t="n"/>
       <c r="AB203" s="28" t="n"/>
-      <c r="AC203" s="30" t="n"/>
-      <c r="AD203" s="24" t="n"/>
+      <c r="AC203" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD203" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:22.970105Z</t>
+        </is>
+      </c>
       <c r="AE203" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.4100 (market_slug=aec-npb-tys-hci-2026-10-04). Tie probability=0.0238.</t>
@@ -65205,7 +65421,7 @@
       </c>
       <c r="AG203" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH203" s="24" t="n"/>
@@ -65482,18 +65698,32 @@
       </c>
       <c r="U204" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V204" s="24" t="n"/>
-      <c r="W204" s="26" t="n"/>
-      <c r="X204" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V204" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W204" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X204" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="Y204" s="25" t="n"/>
       <c r="Z204" s="26" t="n"/>
       <c r="AA204" s="28" t="n"/>
       <c r="AB204" s="28" t="n"/>
-      <c r="AC204" s="30" t="n"/>
-      <c r="AD204" s="24" t="n"/>
+      <c r="AC204" s="30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD204" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:24.577992Z</t>
+        </is>
+      </c>
       <c r="AE204" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.4900 (market_slug=aec-npb-clm-trge-2026-10-04). Tie probability=0.0238.</t>
@@ -65783,18 +66013,32 @@
       </c>
       <c r="U205" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V205" s="24" t="n"/>
-      <c r="W205" s="26" t="n"/>
-      <c r="X205" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V205" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W205" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="X205" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y205" s="25" t="n"/>
       <c r="Z205" s="26" t="n"/>
       <c r="AA205" s="28" t="n"/>
       <c r="AB205" s="28" t="n"/>
-      <c r="AC205" s="30" t="n"/>
-      <c r="AD205" s="24" t="n"/>
+      <c r="AC205" s="30" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+      <c r="AD205" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:26.220789Z</t>
+        </is>
+      </c>
       <c r="AE205" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5200 (market_slug=aec-npb-clm-ssl-2026-10-05). Tie probability=0.0238.</t>
@@ -66080,18 +66324,32 @@
       </c>
       <c r="U206" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V206" s="24" t="n"/>
-      <c r="W206" s="26" t="n"/>
-      <c r="X206" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V206" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W206" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X206" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="Y206" s="25" t="n"/>
       <c r="Z206" s="26" t="n"/>
       <c r="AA206" s="28" t="n"/>
       <c r="AB206" s="28" t="n"/>
-      <c r="AC206" s="30" t="n"/>
-      <c r="AD206" s="24" t="n"/>
+      <c r="AC206" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD206" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:27.778952Z</t>
+        </is>
+      </c>
       <c r="AE206" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5900 (market_slug=aec-npb-trge-fsh-2026-10-05). Tie probability=0.0238.</t>
@@ -66104,7 +66362,7 @@
       </c>
       <c r="AG206" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH206" s="24" t="n"/>
@@ -66377,18 +66635,32 @@
       </c>
       <c r="U207" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V207" s="24" t="n"/>
-      <c r="W207" s="26" t="n"/>
-      <c r="X207" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V207" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W207" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X207" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y207" s="25" t="n"/>
       <c r="Z207" s="26" t="n"/>
       <c r="AA207" s="28" t="n"/>
       <c r="AB207" s="28" t="n"/>
-      <c r="AC207" s="30" t="n"/>
-      <c r="AD207" s="24" t="n"/>
+      <c r="AC207" s="30" t="n">
+        <v>0.8197</v>
+      </c>
+      <c r="AD207" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:29.390858Z</t>
+        </is>
+      </c>
       <c r="AE207" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-npb-clm-ssl-2026-10-06). Tie probability=0.0238.</t>
@@ -66674,18 +66946,32 @@
       </c>
       <c r="U208" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V208" s="24" t="n"/>
-      <c r="W208" s="26" t="n"/>
-      <c r="X208" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V208" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W208" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X208" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y208" s="25" t="n"/>
       <c r="Z208" s="26" t="n"/>
       <c r="AA208" s="28" t="n"/>
       <c r="AB208" s="28" t="n"/>
-      <c r="AC208" s="30" t="n"/>
-      <c r="AD208" s="24" t="n"/>
+      <c r="AC208" s="30" t="n">
+        <v>0.5618</v>
+      </c>
+      <c r="AD208" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:30.895501Z</t>
+        </is>
+      </c>
       <c r="AE208" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6400 (market_slug=aec-npb-hta-hci-2026-10-06). Tie probability=0.0238.</t>
@@ -66890,6 +67176,303 @@
         </is>
       </c>
     </row>
+    <row r="209" ht="36" customHeight="1">
+      <c r="A209" s="24" t="inlineStr">
+        <is>
+          <t>9c22b7354c3b47ee</t>
+        </is>
+      </c>
+      <c r="B209" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:24:50.453102Z</t>
+        </is>
+      </c>
+      <c r="C209" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D209" s="24" t="inlineStr">
+        <is>
+          <t>142741</t>
+        </is>
+      </c>
+      <c r="E209" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F209" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="G209" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="H209" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I209" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J209" s="25" t="n"/>
+      <c r="K209" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L209" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M209" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N209" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O209" s="28" t="n">
+        <v>0.652882</v>
+      </c>
+      <c r="P209" s="28" t="n"/>
+      <c r="Q209" s="28" t="n">
+        <v>0.043507</v>
+      </c>
+      <c r="R209" s="26" t="n">
+        <v>42</v>
+      </c>
+      <c r="S209" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T209" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U209" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V209" s="24" t="n"/>
+      <c r="W209" s="26" t="n"/>
+      <c r="X209" s="26" t="n"/>
+      <c r="Y209" s="25" t="n"/>
+      <c r="Z209" s="26" t="n"/>
+      <c r="AA209" s="28" t="n"/>
+      <c r="AB209" s="28" t="n"/>
+      <c r="AC209" s="30" t="n"/>
+      <c r="AD209" s="24" t="n"/>
+      <c r="AE209" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-hta-hci-2026-10-07). Tie probability=0.0238.</t>
+        </is>
+      </c>
+      <c r="AF209" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG209" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH209" s="24" t="n"/>
+      <c r="AI209" s="31" t="n"/>
+      <c r="AJ209" s="31" t="n"/>
+      <c r="AK209" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL209" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM209" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN209" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO209" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP209" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AQ209" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AR209" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AS209" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AT209" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AU209" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AV209" s="24" t="n"/>
+      <c r="AW209" s="24" t="n"/>
+      <c r="AX209" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY209" s="24" t="n"/>
+      <c r="AZ209" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA209" s="24" t="inlineStr">
+        <is>
+          <t>52a745e24a739f7876c425755afd5d949b082851299aad8a723cad3af868096f</t>
+        </is>
+      </c>
+      <c r="BB209" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC209" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD209" s="24" t="inlineStr">
+        <is>
+          <t>52a745e24a739f7876c425755afd5d949b082851299aad8a723cad3af868096f</t>
+        </is>
+      </c>
+      <c r="BE209" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF209" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG209" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH209" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:24:50.452100Z</t>
+        </is>
+      </c>
+      <c r="BI209" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ209" s="25" t="n"/>
+      <c r="BK209" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL209" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM209" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN209" s="28" t="n"/>
+      <c r="BO209" s="28" t="n"/>
+      <c r="BP209" s="25" t="n"/>
+      <c r="BQ209" s="27" t="n"/>
+      <c r="BR209" s="28" t="n"/>
+      <c r="BS209" s="28" t="n"/>
+      <c r="BT209" s="28" t="n"/>
+      <c r="BU209" s="25" t="n"/>
+      <c r="BV209" s="29" t="n"/>
+      <c r="BW209" s="24" t="n"/>
+      <c r="BX209" s="30" t="n"/>
+      <c r="BY209" s="27" t="n"/>
+      <c r="BZ209" s="24" t="n"/>
+      <c r="CA209" s="31" t="n"/>
+      <c r="CB209" s="24" t="n"/>
+      <c r="CC209" s="24" t="n"/>
+      <c r="CD209" s="24" t="n"/>
+      <c r="CE209" s="24" t="n"/>
+      <c r="CF209" s="24" t="n"/>
+      <c r="CG209" s="24" t="n"/>
+      <c r="CH209" s="24" t="n"/>
+      <c r="CI209" s="24" t="n"/>
+      <c r="CJ209" s="24" t="n"/>
+      <c r="CK209" s="24" t="n"/>
+      <c r="CL209" s="24" t="n"/>
+      <c r="CM209" s="24" t="n"/>
+      <c r="CN209" s="24" t="n"/>
+      <c r="CO209" s="24" t="n"/>
+      <c r="CP209" s="24" t="n"/>
+      <c r="CQ209" s="24" t="n"/>
+      <c r="CR209" s="24" t="n"/>
+      <c r="CS209" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT209" s="24" t="n"/>
+      <c r="CU209" s="24" t="n"/>
+      <c r="CV209" s="24" t="n"/>
+      <c r="CW209" s="24" t="n"/>
+      <c r="CX209" s="24" t="n"/>
+      <c r="CY209" s="24" t="n"/>
+      <c r="CZ209" s="24" t="n"/>
+      <c r="DA209" s="24" t="n"/>
+      <c r="DB209" s="24" t="n"/>
+      <c r="DC209" s="24" t="n"/>
+      <c r="DD209" s="24" t="n"/>
+      <c r="DE209" s="24" t="n"/>
+      <c r="DF209" s="24" t="n"/>
+      <c r="DG209" s="24" t="n"/>
+      <c r="DH209" s="24" t="n"/>
+      <c r="DI209" s="24" t="n"/>
+      <c r="DJ209" s="24" t="n"/>
+      <c r="DK209" s="24" t="n"/>
+      <c r="DL209" s="24" t="n"/>
+      <c r="DM209" s="24" t="n"/>
+      <c r="DN209" s="24" t="n"/>
+      <c r="DO209" s="24" t="n"/>
+      <c r="DP209" s="24" t="n"/>
+      <c r="DQ209" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "52a745e24a739f7876c425755afd5d949b082851299aad8a723cad3af868096f", "away_team": "Hiroshima Carp", "draw_settlement_value": 0.5, "event_id": "142741", "event_start_utc": "2026-10-07T09:00:00Z", "features": {"away_elo": 1450.602544, "base_tie_rate": 0.02376426, "home_advantage": 35.0, "home_elo": 1528.205664}, "historical_source_observation_times_verified": false, "home_team": "Hanshin Tigers", "inference_inputs": {"away_id": "C", "base_tie_rate": 0.02376426, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"C": 1450.602544, "T": 1528.205664}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "f345eb917316d2e897f62c1cdd0f73153115c65da54c30c6137ad76bb7b27869"}, "home_id": "T", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-06T22:24:50.368130+00:00", "outcome_probabilities": {"away": 0.33523569757097316, "draw": 0.02376426, "home": 0.6410000424290269}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.347118, "home": 0.652882}, "snapshot_hash": "18ad0541cfa33136696305362d5830825eab9db052c43c2c564477afb450c425", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/sports/npb/research.xlsx
+++ b/data/sports/npb/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ209" headerRowCount="1">
-  <autoFilter ref="A1:DQ209"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ215" headerRowCount="1">
+  <autoFilter ref="A1:DQ215"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$209)</f>
+        <f>COUNTA('Picks'!$A$2:$A$215)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$209,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$215,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$209,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$215,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$209,"settled",'Picks'!$V$2:$V$209,"win")+COUNTIFS('Picks'!$U$2:$U$209,"settled",'Picks'!$V$2:$V$209,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"win")+COUNTIFS('Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$209,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$215,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$209,"&gt;0",'Picks'!$V$2:$V$209,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$209,"&gt;0",'Picks'!$V$2:$V$209,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$209,"&gt;0",'Picks'!$V$2:$V$209,"win")/(COUNTIFS('Picks'!$BX$2:$BX$209,"&gt;0",'Picks'!$V$2:$V$209,"win")+COUNTIFS('Picks'!$BX$2:$BX$209,"&gt;0",'Picks'!$V$2:$V$209,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"win")/(COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"win")+COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$209)/SUM('Picks'!$BX$2:$BX$209),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$215)/SUM('Picks'!$BX$2:$BX$215),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$209)</f>
+        <f>SUM('Picks'!$BY$2:$BY$215)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$209,"&lt;&gt;",'Picks'!$AB$2:$AB$209),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$215,"&lt;&gt;",'Picks'!$AB$2:$AB$215),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$209,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$209,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$215,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$215,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$209,'Picks'!$AM$2:$AM$209,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$215,'Picks'!$AM$2:$AM$215,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$209,$A14,'Picks'!$U$2:$U$209,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A14,'Picks'!$U$2:$U$215,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$209,$A14,'Picks'!$U$2:$U$209,"settled",'Picks'!$V$2:$V$209,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A14,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$209,$A14,'Picks'!$U$2:$U$209,"settled",'Picks'!$V$2:$V$209,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A14,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$209,'Picks'!$H$2:$H$209,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$215,'Picks'!$H$2:$H$215,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$209,'Picks'!$H$2:$H$209,$A14,'Picks'!$U$2:$U$209,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$215,'Picks'!$H$2:$H$215,$A14,'Picks'!$U$2:$U$215,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$209,$A15,'Picks'!$U$2:$U$209,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A15,'Picks'!$U$2:$U$215,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$209,$A15,'Picks'!$U$2:$U$209,"settled",'Picks'!$V$2:$V$209,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A15,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$209,$A15,'Picks'!$U$2:$U$209,"settled",'Picks'!$V$2:$V$209,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A15,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$209,'Picks'!$H$2:$H$209,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$215,'Picks'!$H$2:$H$215,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$209,'Picks'!$H$2:$H$209,$A15,'Picks'!$U$2:$U$209,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$215,'Picks'!$H$2:$H$215,$A15,'Picks'!$U$2:$U$215,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$209,$A16,'Picks'!$U$2:$U$209,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A16,'Picks'!$U$2:$U$215,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$209,$A16,'Picks'!$U$2:$U$209,"settled",'Picks'!$V$2:$V$209,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A16,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$209,$A16,'Picks'!$U$2:$U$209,"settled",'Picks'!$V$2:$V$209,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A16,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$209,'Picks'!$H$2:$H$209,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$215,'Picks'!$H$2:$H$215,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$209,'Picks'!$H$2:$H$209,$A16,'Picks'!$U$2:$U$209,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$215,'Picks'!$H$2:$H$215,$A16,'Picks'!$U$2:$U$215,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ209"/>
+  <dimension ref="A1:DQ215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -67179,12 +67179,12 @@
     <row r="209" ht="36" customHeight="1">
       <c r="A209" s="24" t="inlineStr">
         <is>
-          <t>9c22b7354c3b47ee</t>
+          <t>1d7c03d841d1419b</t>
         </is>
       </c>
       <c r="B209" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:24:50.453102Z</t>
+          <t>2026-10-07T05:28:32.825150Z</t>
         </is>
       </c>
       <c r="C209" s="24" t="inlineStr">
@@ -67229,23 +67229,23 @@
         </is>
       </c>
       <c r="L209" s="26" t="n">
-        <v>-156</v>
+        <v>-150</v>
       </c>
       <c r="M209" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.666667</v>
       </c>
       <c r="N209" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.6</v>
       </c>
       <c r="O209" s="28" t="n">
-        <v>0.652882</v>
+        <v>0.6338279999999999</v>
       </c>
       <c r="P209" s="28" t="n"/>
       <c r="Q209" s="28" t="n">
-        <v>0.043507</v>
+        <v>0.033828</v>
       </c>
       <c r="R209" s="26" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="S209" s="29" t="n">
         <v>1</v>
@@ -67257,21 +67257,41 @@
       </c>
       <c r="U209" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V209" s="24" t="n"/>
-      <c r="W209" s="26" t="n"/>
-      <c r="X209" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V209" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W209" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X209" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y209" s="25" t="n"/>
-      <c r="Z209" s="26" t="n"/>
-      <c r="AA209" s="28" t="n"/>
-      <c r="AB209" s="28" t="n"/>
-      <c r="AC209" s="30" t="n"/>
-      <c r="AD209" s="24" t="n"/>
+      <c r="Z209" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="AA209" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB209" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC209" s="30" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AD209" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:03:14.193640Z</t>
+        </is>
+      </c>
       <c r="AE209" s="31" t="inlineStr">
         <is>
-          <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-hta-hci-2026-10-07). Tie probability=0.0238.</t>
+          <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-npb-hta-hci-2026-10-07). Tie probability=0.0239.</t>
         </is>
       </c>
       <c r="AF209" s="31" t="inlineStr">
@@ -67355,7 +67375,7 @@
       </c>
       <c r="BA209" s="24" t="inlineStr">
         <is>
-          <t>52a745e24a739f7876c425755afd5d949b082851299aad8a723cad3af868096f</t>
+          <t>68d07ee48d1509bcf95582a676d54274539f6ebe66c40e274ab6c8ab22373648</t>
         </is>
       </c>
       <c r="BB209" s="24" t="inlineStr">
@@ -67370,7 +67390,7 @@
       </c>
       <c r="BD209" s="24" t="inlineStr">
         <is>
-          <t>52a745e24a739f7876c425755afd5d949b082851299aad8a723cad3af868096f</t>
+          <t>68d07ee48d1509bcf95582a676d54274539f6ebe66c40e274ab6c8ab22373648</t>
         </is>
       </c>
       <c r="BE209" s="24" t="inlineStr">
@@ -67390,7 +67410,7 @@
       </c>
       <c r="BH209" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:24:50.452100Z</t>
+          <t>2026-10-07T05:28:32.825150Z</t>
         </is>
       </c>
       <c r="BI209" s="24" t="inlineStr">
@@ -67400,19 +67420,23 @@
       </c>
       <c r="BJ209" s="25" t="n"/>
       <c r="BK209" s="26" t="n">
-        <v>-156</v>
+        <v>-150</v>
       </c>
       <c r="BL209" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.666667</v>
       </c>
       <c r="BM209" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.6</v>
       </c>
       <c r="BN209" s="28" t="n"/>
       <c r="BO209" s="28" t="n"/>
       <c r="BP209" s="25" t="n"/>
-      <c r="BQ209" s="27" t="n"/>
-      <c r="BR209" s="28" t="n"/>
+      <c r="BQ209" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BR209" s="28" t="n">
+        <v>0.6</v>
+      </c>
       <c r="BS209" s="28" t="n"/>
       <c r="BT209" s="28" t="n"/>
       <c r="BU209" s="25" t="n"/>
@@ -67469,7 +67493,1845 @@
       <c r="DP209" s="24" t="n"/>
       <c r="DQ209" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "52a745e24a739f7876c425755afd5d949b082851299aad8a723cad3af868096f", "away_team": "Hiroshima Carp", "draw_settlement_value": 0.5, "event_id": "142741", "event_start_utc": "2026-10-07T09:00:00Z", "features": {"away_elo": 1450.602544, "base_tie_rate": 0.02376426, "home_advantage": 35.0, "home_elo": 1528.205664}, "historical_source_observation_times_verified": false, "home_team": "Hanshin Tigers", "inference_inputs": {"away_id": "C", "base_tie_rate": 0.02376426, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"C": 1450.602544, "T": 1528.205664}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "f345eb917316d2e897f62c1cdd0f73153115c65da54c30c6137ad76bb7b27869"}, "home_id": "T", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-06T22:24:50.368130+00:00", "outcome_probabilities": {"away": 0.33523569757097316, "draw": 0.02376426, "home": 0.6410000424290269}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.347118, "home": 0.652882}, "snapshot_hash": "18ad0541cfa33136696305362d5830825eab9db052c43c2c564477afb450c425", "sport": "NPB"}</t>
+          <t>{"artifact_hash": "68d07ee48d1509bcf95582a676d54274539f6ebe66c40e274ab6c8ab22373648", "away_team": "Hiroshima Carp", "draw_settlement_value": 0.5, "event_id": "142741", "event_start_utc": "2026-10-07T09:00:00Z", "features": {"away_elo": 1459.619403, "base_tie_rate": 0.02389967, "home_advantage": 35.0, "home_elo": 1522.390934}, "historical_source_observation_times_verified": false, "home_team": "Hanshin Tigers", "inference_inputs": {"away_id": "C", "base_tie_rate": 0.02389967, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"C": 1459.619403, "T": 1522.390934}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "58ea522476e21dc70a719fe60647c19a772fcb4703fef8ed2d47c4ba7f07c2d5"}, "home_id": "T", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-07T05:28:32.688023+00:00", "outcome_probabilities": {"away": 0.35422255357395394, "draw": 0.02389967, "home": 0.621877776426046}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.366172, "home": 0.633828}, "snapshot_hash": "87cf5b46fdc98e6724511cbd171f17824be2c7e42a1ccf8425aebafdb60d7db5", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="36" customHeight="1">
+      <c r="A210" s="24" t="inlineStr">
+        <is>
+          <t>51e8d642800f4892</t>
+        </is>
+      </c>
+      <c r="B210" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:27:05.714336Z</t>
+        </is>
+      </c>
+      <c r="C210" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D210" s="24" t="inlineStr">
+        <is>
+          <t>144497</t>
+        </is>
+      </c>
+      <c r="E210" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F210" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="G210" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="H210" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I210" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J210" s="25" t="n"/>
+      <c r="K210" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L210" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M210" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N210" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O210" s="28" t="n">
+        <v>0.691636</v>
+      </c>
+      <c r="P210" s="28" t="n"/>
+      <c r="Q210" s="28" t="n">
+        <v>0.051348</v>
+      </c>
+      <c r="R210" s="26" t="n">
+        <v>46</v>
+      </c>
+      <c r="S210" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T210" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U210" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V210" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W210" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X210" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y210" s="25" t="n"/>
+      <c r="Z210" s="26" t="n"/>
+      <c r="AA210" s="28" t="n"/>
+      <c r="AB210" s="28" t="n"/>
+      <c r="AC210" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD210" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T04:37:10.205236Z</t>
+        </is>
+      </c>
+      <c r="AE210" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6400 (market_slug=aec-npb-hta-tys-2026-10-08). Tie probability=0.0239.</t>
+        </is>
+      </c>
+      <c r="AF210" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG210" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH210" s="24" t="n"/>
+      <c r="AI210" s="31" t="n"/>
+      <c r="AJ210" s="31" t="n"/>
+      <c r="AK210" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL210" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM210" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN210" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO210" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP210" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AQ210" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AR210" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AS210" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AT210" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AU210" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AV210" s="24" t="n"/>
+      <c r="AW210" s="24" t="n"/>
+      <c r="AX210" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY210" s="24" t="n"/>
+      <c r="AZ210" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA210" s="24" t="inlineStr">
+        <is>
+          <t>b308d622b430a23c8c792fdf24eacf1319adf7cdec74fedf9555576e3842e388</t>
+        </is>
+      </c>
+      <c r="BB210" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC210" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD210" s="24" t="inlineStr">
+        <is>
+          <t>b308d622b430a23c8c792fdf24eacf1319adf7cdec74fedf9555576e3842e388</t>
+        </is>
+      </c>
+      <c r="BE210" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF210" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG210" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH210" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:27:05.714336Z</t>
+        </is>
+      </c>
+      <c r="BI210" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ210" s="25" t="n"/>
+      <c r="BK210" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL210" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM210" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN210" s="28" t="n"/>
+      <c r="BO210" s="28" t="n"/>
+      <c r="BP210" s="25" t="n"/>
+      <c r="BQ210" s="27" t="n"/>
+      <c r="BR210" s="28" t="n"/>
+      <c r="BS210" s="28" t="n"/>
+      <c r="BT210" s="28" t="n"/>
+      <c r="BU210" s="25" t="n"/>
+      <c r="BV210" s="29" t="n"/>
+      <c r="BW210" s="24" t="n"/>
+      <c r="BX210" s="30" t="n"/>
+      <c r="BY210" s="27" t="n"/>
+      <c r="BZ210" s="24" t="n"/>
+      <c r="CA210" s="31" t="n"/>
+      <c r="CB210" s="24" t="n"/>
+      <c r="CC210" s="24" t="n"/>
+      <c r="CD210" s="24" t="n"/>
+      <c r="CE210" s="24" t="n"/>
+      <c r="CF210" s="24" t="n"/>
+      <c r="CG210" s="24" t="n"/>
+      <c r="CH210" s="24" t="n"/>
+      <c r="CI210" s="24" t="n"/>
+      <c r="CJ210" s="24" t="n"/>
+      <c r="CK210" s="24" t="n"/>
+      <c r="CL210" s="24" t="n"/>
+      <c r="CM210" s="24" t="n"/>
+      <c r="CN210" s="24" t="n"/>
+      <c r="CO210" s="24" t="n"/>
+      <c r="CP210" s="24" t="n"/>
+      <c r="CQ210" s="24" t="n"/>
+      <c r="CR210" s="24" t="n"/>
+      <c r="CS210" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT210" s="24" t="n"/>
+      <c r="CU210" s="24" t="n"/>
+      <c r="CV210" s="24" t="n"/>
+      <c r="CW210" s="24" t="n"/>
+      <c r="CX210" s="24" t="n"/>
+      <c r="CY210" s="24" t="n"/>
+      <c r="CZ210" s="24" t="n"/>
+      <c r="DA210" s="24" t="n"/>
+      <c r="DB210" s="24" t="n"/>
+      <c r="DC210" s="24" t="n"/>
+      <c r="DD210" s="24" t="n"/>
+      <c r="DE210" s="24" t="n"/>
+      <c r="DF210" s="24" t="n"/>
+      <c r="DG210" s="24" t="n"/>
+      <c r="DH210" s="24" t="n"/>
+      <c r="DI210" s="24" t="n"/>
+      <c r="DJ210" s="24" t="n"/>
+      <c r="DK210" s="24" t="n"/>
+      <c r="DL210" s="24" t="n"/>
+      <c r="DM210" s="24" t="n"/>
+      <c r="DN210" s="24" t="n"/>
+      <c r="DO210" s="24" t="n"/>
+      <c r="DP210" s="24" t="n"/>
+      <c r="DQ210" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "b308d622b430a23c8c792fdf24eacf1319adf7cdec74fedf9555576e3842e388", "away_team": "Tokyo Yakult Swallows", "draw_settlement_value": 0.5, "event_id": "144497", "event_start_utc": "2026-10-08T09:00:00Z", "features": {"away_elo": 1416.131229, "base_tie_rate": 0.02389401, "home_advantage": 35.0, "home_elo": 1525.294099}, "historical_source_observation_times_verified": false, "home_team": "Hanshin Tigers", "inference_inputs": {"away_id": "S", "base_tie_rate": 0.02389401, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"S": 1416.131229, "T": 1525.294099}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "58ea522476e21dc70a719fe60647c19a772fcb4703fef8ed2d47c4ba7f07c2d5"}, "home_id": "T", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-07T22:27:05.633273+00:00", "outcome_probabilities": {"away": 0.2964169774262092, "draw": 0.02389401, "home": 0.6796890125737908}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.308364, "home": 0.691636}, "snapshot_hash": "f1fb387be0a94b9f162bcc3cdfb4c43a15c021a242d22a9829b2d01dd32a68d8", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="36" customHeight="1">
+      <c r="A211" s="24" t="inlineStr">
+        <is>
+          <t>cb827885e91f4b82</t>
+        </is>
+      </c>
+      <c r="B211" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T01:06:46.457952Z</t>
+        </is>
+      </c>
+      <c r="C211" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D211" s="24" t="inlineStr">
+        <is>
+          <t>148643</t>
+        </is>
+      </c>
+      <c r="E211" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F211" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="G211" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="H211" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I211" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J211" s="25" t="n"/>
+      <c r="K211" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L211" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M211" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N211" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="O211" s="28" t="n">
+        <v>0.537178</v>
+      </c>
+      <c r="P211" s="28" t="n"/>
+      <c r="Q211" s="28" t="n">
+        <v>0.067694</v>
+      </c>
+      <c r="R211" s="26" t="n">
+        <v>54</v>
+      </c>
+      <c r="S211" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T211" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U211" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V211" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W211" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X211" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y211" s="25" t="n"/>
+      <c r="Z211" s="26" t="n"/>
+      <c r="AA211" s="28" t="n"/>
+      <c r="AB211" s="28" t="n"/>
+      <c r="AC211" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD211" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T22:01:57.404973Z</t>
+        </is>
+      </c>
+      <c r="AE211" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4700 (market_slug=aec-npb-ssl-nhf-2026-10-11). Tie probability=0.0239.</t>
+        </is>
+      </c>
+      <c r="AF211" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG211" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH211" s="24" t="n"/>
+      <c r="AI211" s="31" t="n"/>
+      <c r="AJ211" s="31" t="n"/>
+      <c r="AK211" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL211" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM211" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN211" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO211" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP211" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AQ211" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AR211" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AS211" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AT211" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AU211" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AV211" s="24" t="n"/>
+      <c r="AW211" s="24" t="n"/>
+      <c r="AX211" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY211" s="24" t="n"/>
+      <c r="AZ211" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA211" s="24" t="inlineStr">
+        <is>
+          <t>893602d01e5e033b555535a8754105d97c348185ccc30e37513b1c524c69ad79</t>
+        </is>
+      </c>
+      <c r="BB211" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC211" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD211" s="24" t="inlineStr">
+        <is>
+          <t>893602d01e5e033b555535a8754105d97c348185ccc30e37513b1c524c69ad79</t>
+        </is>
+      </c>
+      <c r="BE211" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF211" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG211" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH211" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T01:06:46.403224Z</t>
+        </is>
+      </c>
+      <c r="BI211" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ211" s="25" t="n"/>
+      <c r="BK211" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="BL211" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM211" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="BN211" s="28" t="n"/>
+      <c r="BO211" s="28" t="n"/>
+      <c r="BP211" s="25" t="n"/>
+      <c r="BQ211" s="27" t="n"/>
+      <c r="BR211" s="28" t="n"/>
+      <c r="BS211" s="28" t="n"/>
+      <c r="BT211" s="28" t="n"/>
+      <c r="BU211" s="25" t="n"/>
+      <c r="BV211" s="29" t="n"/>
+      <c r="BW211" s="24" t="n"/>
+      <c r="BX211" s="30" t="n"/>
+      <c r="BY211" s="27" t="n"/>
+      <c r="BZ211" s="24" t="n"/>
+      <c r="CA211" s="31" t="n"/>
+      <c r="CB211" s="24" t="n"/>
+      <c r="CC211" s="24" t="n"/>
+      <c r="CD211" s="24" t="n"/>
+      <c r="CE211" s="24" t="n"/>
+      <c r="CF211" s="24" t="n"/>
+      <c r="CG211" s="24" t="n"/>
+      <c r="CH211" s="24" t="n"/>
+      <c r="CI211" s="24" t="n"/>
+      <c r="CJ211" s="24" t="n"/>
+      <c r="CK211" s="24" t="n"/>
+      <c r="CL211" s="24" t="n"/>
+      <c r="CM211" s="24" t="n"/>
+      <c r="CN211" s="24" t="n"/>
+      <c r="CO211" s="24" t="n"/>
+      <c r="CP211" s="24" t="n"/>
+      <c r="CQ211" s="24" t="n"/>
+      <c r="CR211" s="24" t="n"/>
+      <c r="CS211" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT211" s="24" t="n"/>
+      <c r="CU211" s="24" t="n"/>
+      <c r="CV211" s="24" t="n"/>
+      <c r="CW211" s="24" t="n"/>
+      <c r="CX211" s="24" t="n"/>
+      <c r="CY211" s="24" t="n"/>
+      <c r="CZ211" s="24" t="n"/>
+      <c r="DA211" s="24" t="n"/>
+      <c r="DB211" s="24" t="n"/>
+      <c r="DC211" s="24" t="n"/>
+      <c r="DD211" s="24" t="n"/>
+      <c r="DE211" s="24" t="n"/>
+      <c r="DF211" s="24" t="n"/>
+      <c r="DG211" s="24" t="n"/>
+      <c r="DH211" s="24" t="n"/>
+      <c r="DI211" s="24" t="n"/>
+      <c r="DJ211" s="24" t="n"/>
+      <c r="DK211" s="24" t="n"/>
+      <c r="DL211" s="24" t="n"/>
+      <c r="DM211" s="24" t="n"/>
+      <c r="DN211" s="24" t="n"/>
+      <c r="DO211" s="24" t="n"/>
+      <c r="DP211" s="24" t="n"/>
+      <c r="DQ211" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "893602d01e5e033b555535a8754105d97c348185ccc30e37513b1c524c69ad79", "away_team": "Nippon Ham Fighters", "draw_settlement_value": 0.5, "event_id": "148643", "event_start_utc": "2026-10-11T05:00:00Z", "features": {"away_elo": 1551.787498, "base_tie_rate": 0.02387707, "home_advantage": 35.0, "home_elo": 1543.304526}, "historical_source_observation_times_verified": false, "home_team": "Saitama Seibu Lions", "inference_inputs": {"away_id": "F", "base_tie_rate": 0.02387707, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"F": 1551.787498, "L": 1543.304526}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "L", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-11T01:06:46.340498+00:00", "outcome_probabilities": {"away": 0.450883728309193, "draw": 0.02387707, "home": 0.5252392016908071}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.462822, "home": 0.537178}, "snapshot_hash": "0adfb8530cd4d68cabea01e26674e27f24c99521898581e14f4074d3b0b3e9fe", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="36" customHeight="1">
+      <c r="A212" s="24" t="inlineStr">
+        <is>
+          <t>5539de7229b243ad</t>
+        </is>
+      </c>
+      <c r="B212" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T01:06:46.457952Z</t>
+        </is>
+      </c>
+      <c r="C212" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D212" s="24" t="inlineStr">
+        <is>
+          <t>148644</t>
+        </is>
+      </c>
+      <c r="E212" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F212" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="G212" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="H212" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I212" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J212" s="25" t="n"/>
+      <c r="K212" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L212" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M212" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N212" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O212" s="28" t="n">
+        <v>0.525257</v>
+      </c>
+      <c r="P212" s="28" t="n"/>
+      <c r="Q212" s="28" t="n">
+        <v>0.035061</v>
+      </c>
+      <c r="R212" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="S212" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T212" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U212" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V212" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W212" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X212" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y212" s="25" t="n"/>
+      <c r="Z212" s="26" t="n"/>
+      <c r="AA212" s="28" t="n"/>
+      <c r="AB212" s="28" t="n"/>
+      <c r="AC212" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD212" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T22:01:59.240893Z</t>
+        </is>
+      </c>
+      <c r="AE212" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4900 (market_slug=aec-npb-ygo-ybo-2026-10-11). Tie probability=0.0239.</t>
+        </is>
+      </c>
+      <c r="AF212" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG212" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH212" s="24" t="n"/>
+      <c r="AI212" s="31" t="n"/>
+      <c r="AJ212" s="31" t="n"/>
+      <c r="AK212" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL212" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM212" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN212" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO212" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP212" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AQ212" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AR212" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AS212" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AT212" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AU212" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AV212" s="24" t="n"/>
+      <c r="AW212" s="24" t="n"/>
+      <c r="AX212" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY212" s="24" t="n"/>
+      <c r="AZ212" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA212" s="24" t="inlineStr">
+        <is>
+          <t>893602d01e5e033b555535a8754105d97c348185ccc30e37513b1c524c69ad79</t>
+        </is>
+      </c>
+      <c r="BB212" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC212" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD212" s="24" t="inlineStr">
+        <is>
+          <t>893602d01e5e033b555535a8754105d97c348185ccc30e37513b1c524c69ad79</t>
+        </is>
+      </c>
+      <c r="BE212" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF212" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG212" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH212" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T01:06:46.457952Z</t>
+        </is>
+      </c>
+      <c r="BI212" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ212" s="25" t="n"/>
+      <c r="BK212" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL212" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM212" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN212" s="28" t="n"/>
+      <c r="BO212" s="28" t="n"/>
+      <c r="BP212" s="25" t="n"/>
+      <c r="BQ212" s="27" t="n"/>
+      <c r="BR212" s="28" t="n"/>
+      <c r="BS212" s="28" t="n"/>
+      <c r="BT212" s="28" t="n"/>
+      <c r="BU212" s="25" t="n"/>
+      <c r="BV212" s="29" t="n"/>
+      <c r="BW212" s="24" t="n"/>
+      <c r="BX212" s="30" t="n"/>
+      <c r="BY212" s="27" t="n"/>
+      <c r="BZ212" s="24" t="n"/>
+      <c r="CA212" s="31" t="n"/>
+      <c r="CB212" s="24" t="n"/>
+      <c r="CC212" s="24" t="n"/>
+      <c r="CD212" s="24" t="n"/>
+      <c r="CE212" s="24" t="n"/>
+      <c r="CF212" s="24" t="n"/>
+      <c r="CG212" s="24" t="n"/>
+      <c r="CH212" s="24" t="n"/>
+      <c r="CI212" s="24" t="n"/>
+      <c r="CJ212" s="24" t="n"/>
+      <c r="CK212" s="24" t="n"/>
+      <c r="CL212" s="24" t="n"/>
+      <c r="CM212" s="24" t="n"/>
+      <c r="CN212" s="24" t="n"/>
+      <c r="CO212" s="24" t="n"/>
+      <c r="CP212" s="24" t="n"/>
+      <c r="CQ212" s="24" t="n"/>
+      <c r="CR212" s="24" t="n"/>
+      <c r="CS212" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT212" s="24" t="n"/>
+      <c r="CU212" s="24" t="n"/>
+      <c r="CV212" s="24" t="n"/>
+      <c r="CW212" s="24" t="n"/>
+      <c r="CX212" s="24" t="n"/>
+      <c r="CY212" s="24" t="n"/>
+      <c r="CZ212" s="24" t="n"/>
+      <c r="DA212" s="24" t="n"/>
+      <c r="DB212" s="24" t="n"/>
+      <c r="DC212" s="24" t="n"/>
+      <c r="DD212" s="24" t="n"/>
+      <c r="DE212" s="24" t="n"/>
+      <c r="DF212" s="24" t="n"/>
+      <c r="DG212" s="24" t="n"/>
+      <c r="DH212" s="24" t="n"/>
+      <c r="DI212" s="24" t="n"/>
+      <c r="DJ212" s="24" t="n"/>
+      <c r="DK212" s="24" t="n"/>
+      <c r="DL212" s="24" t="n"/>
+      <c r="DM212" s="24" t="n"/>
+      <c r="DN212" s="24" t="n"/>
+      <c r="DO212" s="24" t="n"/>
+      <c r="DP212" s="24" t="n"/>
+      <c r="DQ212" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "893602d01e5e033b555535a8754105d97c348185ccc30e37513b1c524c69ad79", "away_team": "Yokohama BayStars", "draw_settlement_value": 0.5, "event_id": "148644", "event_start_utc": "2026-10-11T05:00:00Z", "features": {"away_elo": 1516.853935, "base_tie_rate": 0.02387707, "home_advantage": 35.0, "home_elo": 1499.849559}, "historical_source_observation_times_verified": false, "home_team": "Yomiuri Giants", "inference_inputs": {"away_id": "DB", "base_tie_rate": 0.02387707, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"DB": 1516.853935, "G": 1499.849559}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "G", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-11T01:06:46.340498+00:00", "outcome_probabilities": {"away": 0.4628046256439446, "draw": 0.02387707, "home": 0.5133183043560555}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.474743, "home": 0.525257}, "snapshot_hash": "3b835560ef63bf24f261f0734a60c05f92b317cc06babf16f710ccdfe5a46891", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="36" customHeight="1">
+      <c r="A213" s="24" t="inlineStr">
+        <is>
+          <t>8c80f2db87ab4ca2</t>
+        </is>
+      </c>
+      <c r="B213" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T22:38:31.027034Z</t>
+        </is>
+      </c>
+      <c r="C213" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D213" s="24" t="inlineStr">
+        <is>
+          <t>154782</t>
+        </is>
+      </c>
+      <c r="E213" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F213" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="G213" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="H213" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I213" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J213" s="25" t="n"/>
+      <c r="K213" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L213" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M213" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N213" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O213" s="28" t="n">
+        <v>0.525134</v>
+      </c>
+      <c r="P213" s="28" t="n"/>
+      <c r="Q213" s="28" t="n">
+        <v>-0.014037</v>
+      </c>
+      <c r="R213" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="S213" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T213" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U213" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V213" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W213" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X213" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y213" s="25" t="n"/>
+      <c r="Z213" s="26" t="n"/>
+      <c r="AA213" s="28" t="n"/>
+      <c r="AB213" s="28" t="n"/>
+      <c r="AC213" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD213" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T22:03:31.738539Z</t>
+        </is>
+      </c>
+      <c r="AE213" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5400 (market_slug=aec-npb-ssl-nhf-2026-10-12). Tie probability=0.0239.</t>
+        </is>
+      </c>
+      <c r="AF213" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG213" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH213" s="24" t="n"/>
+      <c r="AI213" s="31" t="n"/>
+      <c r="AJ213" s="31" t="n"/>
+      <c r="AK213" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL213" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM213" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN213" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO213" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP213" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AQ213" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AR213" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AS213" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AT213" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AU213" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AV213" s="24" t="n"/>
+      <c r="AW213" s="24" t="n"/>
+      <c r="AX213" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY213" s="24" t="n"/>
+      <c r="AZ213" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA213" s="24" t="inlineStr">
+        <is>
+          <t>b1442f66b73b82e842e6c57616754b46017f10f0e356edc8600ad4d6610cda2f</t>
+        </is>
+      </c>
+      <c r="BB213" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC213" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD213" s="24" t="inlineStr">
+        <is>
+          <t>b1442f66b73b82e842e6c57616754b46017f10f0e356edc8600ad4d6610cda2f</t>
+        </is>
+      </c>
+      <c r="BE213" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF213" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG213" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH213" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T22:38:31.026029Z</t>
+        </is>
+      </c>
+      <c r="BI213" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ213" s="25" t="n"/>
+      <c r="BK213" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL213" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM213" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN213" s="28" t="n"/>
+      <c r="BO213" s="28" t="n"/>
+      <c r="BP213" s="25" t="n"/>
+      <c r="BQ213" s="27" t="n"/>
+      <c r="BR213" s="28" t="n"/>
+      <c r="BS213" s="28" t="n"/>
+      <c r="BT213" s="28" t="n"/>
+      <c r="BU213" s="25" t="n"/>
+      <c r="BV213" s="29" t="n"/>
+      <c r="BW213" s="24" t="n"/>
+      <c r="BX213" s="30" t="n"/>
+      <c r="BY213" s="27" t="n"/>
+      <c r="BZ213" s="24" t="n"/>
+      <c r="CA213" s="31" t="n"/>
+      <c r="CB213" s="24" t="n"/>
+      <c r="CC213" s="24" t="n"/>
+      <c r="CD213" s="24" t="n"/>
+      <c r="CE213" s="24" t="n"/>
+      <c r="CF213" s="24" t="n"/>
+      <c r="CG213" s="24" t="n"/>
+      <c r="CH213" s="24" t="n"/>
+      <c r="CI213" s="24" t="n"/>
+      <c r="CJ213" s="24" t="n"/>
+      <c r="CK213" s="24" t="n"/>
+      <c r="CL213" s="24" t="n"/>
+      <c r="CM213" s="24" t="n"/>
+      <c r="CN213" s="24" t="n"/>
+      <c r="CO213" s="24" t="n"/>
+      <c r="CP213" s="24" t="n"/>
+      <c r="CQ213" s="24" t="n"/>
+      <c r="CR213" s="24" t="n"/>
+      <c r="CS213" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT213" s="24" t="n"/>
+      <c r="CU213" s="24" t="n"/>
+      <c r="CV213" s="24" t="n"/>
+      <c r="CW213" s="24" t="n"/>
+      <c r="CX213" s="24" t="n"/>
+      <c r="CY213" s="24" t="n"/>
+      <c r="CZ213" s="24" t="n"/>
+      <c r="DA213" s="24" t="n"/>
+      <c r="DB213" s="24" t="n"/>
+      <c r="DC213" s="24" t="n"/>
+      <c r="DD213" s="24" t="n"/>
+      <c r="DE213" s="24" t="n"/>
+      <c r="DF213" s="24" t="n"/>
+      <c r="DG213" s="24" t="n"/>
+      <c r="DH213" s="24" t="n"/>
+      <c r="DI213" s="24" t="n"/>
+      <c r="DJ213" s="24" t="n"/>
+      <c r="DK213" s="24" t="n"/>
+      <c r="DL213" s="24" t="n"/>
+      <c r="DM213" s="24" t="n"/>
+      <c r="DN213" s="24" t="n"/>
+      <c r="DO213" s="24" t="n"/>
+      <c r="DP213" s="24" t="n"/>
+      <c r="DQ213" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "b1442f66b73b82e842e6c57616754b46017f10f0e356edc8600ad4d6610cda2f", "away_team": "Nippon Ham Fighters", "draw_settlement_value": 0.5, "event_id": "154782", "event_start_utc": "2026-10-12T05:00:00Z", "features": {"away_elo": 1556.092195, "base_tie_rate": 0.02386578, "home_advantage": 35.0, "home_elo": 1538.999828}, "historical_source_observation_times_verified": false, "home_team": "Saitama Seibu Lions", "inference_inputs": {"away_id": "F", "base_tie_rate": 0.02386578, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"F": 1556.092195, "L": 1538.999828}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "L", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-11T22:38:26.630105+00:00", "outcome_probabilities": {"away": 0.46293325623630444, "draw": 0.02386578, "home": 0.5132009637636956}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.474866, "home": 0.525134}, "snapshot_hash": "e7ed6afe98bfebdb9e5fb4b2aaaee8218eb1507832c8782d3e4baa9d3c420c27", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="36" customHeight="1">
+      <c r="A214" s="24" t="inlineStr">
+        <is>
+          <t>4d9e53576bd2462b</t>
+        </is>
+      </c>
+      <c r="B214" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:28:52.203222Z</t>
+        </is>
+      </c>
+      <c r="C214" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D214" s="24" t="inlineStr">
+        <is>
+          <t>154783</t>
+        </is>
+      </c>
+      <c r="E214" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F214" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="G214" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="H214" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I214" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J214" s="25" t="n"/>
+      <c r="K214" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L214" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M214" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N214" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O214" s="28" t="n">
+        <v>0.547141</v>
+      </c>
+      <c r="P214" s="28" t="n"/>
+      <c r="Q214" s="28" t="n">
+        <v>-0.052859</v>
+      </c>
+      <c r="R214" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T214" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U214" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V214" s="24" t="n"/>
+      <c r="W214" s="26" t="n"/>
+      <c r="X214" s="26" t="n"/>
+      <c r="Y214" s="25" t="n"/>
+      <c r="Z214" s="26" t="n"/>
+      <c r="AA214" s="28" t="n"/>
+      <c r="AB214" s="28" t="n"/>
+      <c r="AC214" s="30" t="n"/>
+      <c r="AD214" s="24" t="n"/>
+      <c r="AE214" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-npb-hta-ybo-2026-10-14). Tie probability=0.0239.</t>
+        </is>
+      </c>
+      <c r="AF214" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG214" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH214" s="24" t="n"/>
+      <c r="AI214" s="31" t="n"/>
+      <c r="AJ214" s="31" t="n"/>
+      <c r="AK214" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL214" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM214" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN214" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO214" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP214" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AQ214" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AR214" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AS214" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AT214" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AU214" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AV214" s="24" t="n"/>
+      <c r="AW214" s="24" t="n"/>
+      <c r="AX214" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY214" s="24" t="n"/>
+      <c r="AZ214" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA214" s="24" t="inlineStr">
+        <is>
+          <t>22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7</t>
+        </is>
+      </c>
+      <c r="BB214" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC214" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD214" s="24" t="inlineStr">
+        <is>
+          <t>22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7</t>
+        </is>
+      </c>
+      <c r="BE214" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF214" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG214" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH214" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:28:51.878028Z</t>
+        </is>
+      </c>
+      <c r="BI214" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ214" s="25" t="n"/>
+      <c r="BK214" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL214" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM214" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN214" s="28" t="n"/>
+      <c r="BO214" s="28" t="n"/>
+      <c r="BP214" s="25" t="n"/>
+      <c r="BQ214" s="27" t="n"/>
+      <c r="BR214" s="28" t="n"/>
+      <c r="BS214" s="28" t="n"/>
+      <c r="BT214" s="28" t="n"/>
+      <c r="BU214" s="25" t="n"/>
+      <c r="BV214" s="29" t="n"/>
+      <c r="BW214" s="24" t="n"/>
+      <c r="BX214" s="30" t="n"/>
+      <c r="BY214" s="27" t="n"/>
+      <c r="BZ214" s="24" t="n"/>
+      <c r="CA214" s="31" t="n"/>
+      <c r="CB214" s="24" t="n"/>
+      <c r="CC214" s="24" t="n"/>
+      <c r="CD214" s="24" t="n"/>
+      <c r="CE214" s="24" t="n"/>
+      <c r="CF214" s="24" t="n"/>
+      <c r="CG214" s="24" t="n"/>
+      <c r="CH214" s="24" t="n"/>
+      <c r="CI214" s="24" t="n"/>
+      <c r="CJ214" s="24" t="n"/>
+      <c r="CK214" s="24" t="n"/>
+      <c r="CL214" s="24" t="n"/>
+      <c r="CM214" s="24" t="n"/>
+      <c r="CN214" s="24" t="n"/>
+      <c r="CO214" s="24" t="n"/>
+      <c r="CP214" s="24" t="n"/>
+      <c r="CQ214" s="24" t="n"/>
+      <c r="CR214" s="24" t="n"/>
+      <c r="CS214" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT214" s="24" t="n"/>
+      <c r="CU214" s="24" t="n"/>
+      <c r="CV214" s="24" t="n"/>
+      <c r="CW214" s="24" t="n"/>
+      <c r="CX214" s="24" t="n"/>
+      <c r="CY214" s="24" t="n"/>
+      <c r="CZ214" s="24" t="n"/>
+      <c r="DA214" s="24" t="n"/>
+      <c r="DB214" s="24" t="n"/>
+      <c r="DC214" s="24" t="n"/>
+      <c r="DD214" s="24" t="n"/>
+      <c r="DE214" s="24" t="n"/>
+      <c r="DF214" s="24" t="n"/>
+      <c r="DG214" s="24" t="n"/>
+      <c r="DH214" s="24" t="n"/>
+      <c r="DI214" s="24" t="n"/>
+      <c r="DJ214" s="24" t="n"/>
+      <c r="DK214" s="24" t="n"/>
+      <c r="DL214" s="24" t="n"/>
+      <c r="DM214" s="24" t="n"/>
+      <c r="DN214" s="24" t="n"/>
+      <c r="DO214" s="24" t="n"/>
+      <c r="DP214" s="24" t="n"/>
+      <c r="DQ214" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7", "away_team": "Yokohama BayStars", "draw_settlement_value": 0.5, "event_id": "154783", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1521.060932, "base_tie_rate": 0.02386015, "home_advantage": 35.0, "home_elo": 1519.723482}, "historical_source_observation_times_verified": false, "home_team": "Hanshin Tigers", "inference_inputs": {"away_id": "DB", "base_tie_rate": 0.02386015, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"DB": 1521.060932, "T": 1519.723482}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "T", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-13T22:28:51.412639+00:00", "outcome_probabilities": {"away": 0.4409289279790772, "draw": 0.02386015, "home": 0.5352109220209229}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.452859, "home": 0.547141}, "snapshot_hash": "7015e4880439a4d4afc64cf919c0221dc4d3470b546c8957dd94de8d2f5525ec", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="36" customHeight="1">
+      <c r="A215" s="24" t="inlineStr">
+        <is>
+          <t>7d0a7073fe6d4e19</t>
+        </is>
+      </c>
+      <c r="B215" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:28:52.203222Z</t>
+        </is>
+      </c>
+      <c r="C215" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D215" s="24" t="inlineStr">
+        <is>
+          <t>156784</t>
+        </is>
+      </c>
+      <c r="E215" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F215" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="G215" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="H215" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I215" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J215" s="25" t="n"/>
+      <c r="K215" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L215" s="26" t="n">
+        <v>-270</v>
+      </c>
+      <c r="M215" s="27" t="n">
+        <v>1.37037</v>
+      </c>
+      <c r="N215" s="28" t="n">
+        <v>0.72973</v>
+      </c>
+      <c r="O215" s="28" t="n">
+        <v>0.62865</v>
+      </c>
+      <c r="P215" s="28" t="n"/>
+      <c r="Q215" s="28" t="n">
+        <v>-0.10108</v>
+      </c>
+      <c r="R215" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T215" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U215" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V215" s="24" t="n"/>
+      <c r="W215" s="26" t="n"/>
+      <c r="X215" s="26" t="n"/>
+      <c r="Y215" s="25" t="n"/>
+      <c r="Z215" s="26" t="n"/>
+      <c r="AA215" s="28" t="n"/>
+      <c r="AB215" s="28" t="n"/>
+      <c r="AC215" s="30" t="n"/>
+      <c r="AD215" s="24" t="n"/>
+      <c r="AE215" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.7300 (market_slug=aec-npb-fsh-nhf-2026-10-14). Tie probability=0.0239.</t>
+        </is>
+      </c>
+      <c r="AF215" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG215" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH215" s="24" t="n"/>
+      <c r="AI215" s="31" t="n"/>
+      <c r="AJ215" s="31" t="n"/>
+      <c r="AK215" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL215" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM215" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN215" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO215" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP215" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AQ215" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AR215" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AS215" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AT215" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AU215" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AV215" s="24" t="n"/>
+      <c r="AW215" s="24" t="n"/>
+      <c r="AX215" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY215" s="24" t="n"/>
+      <c r="AZ215" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA215" s="24" t="inlineStr">
+        <is>
+          <t>22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7</t>
+        </is>
+      </c>
+      <c r="BB215" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC215" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD215" s="24" t="inlineStr">
+        <is>
+          <t>22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7</t>
+        </is>
+      </c>
+      <c r="BE215" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF215" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG215" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH215" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:28:52.203222Z</t>
+        </is>
+      </c>
+      <c r="BI215" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ215" s="25" t="n"/>
+      <c r="BK215" s="26" t="n">
+        <v>-270</v>
+      </c>
+      <c r="BL215" s="27" t="n">
+        <v>1.37037</v>
+      </c>
+      <c r="BM215" s="28" t="n">
+        <v>0.72973</v>
+      </c>
+      <c r="BN215" s="28" t="n"/>
+      <c r="BO215" s="28" t="n"/>
+      <c r="BP215" s="25" t="n"/>
+      <c r="BQ215" s="27" t="n"/>
+      <c r="BR215" s="28" t="n"/>
+      <c r="BS215" s="28" t="n"/>
+      <c r="BT215" s="28" t="n"/>
+      <c r="BU215" s="25" t="n"/>
+      <c r="BV215" s="29" t="n"/>
+      <c r="BW215" s="24" t="n"/>
+      <c r="BX215" s="30" t="n"/>
+      <c r="BY215" s="27" t="n"/>
+      <c r="BZ215" s="24" t="n"/>
+      <c r="CA215" s="31" t="n"/>
+      <c r="CB215" s="24" t="n"/>
+      <c r="CC215" s="24" t="n"/>
+      <c r="CD215" s="24" t="n"/>
+      <c r="CE215" s="24" t="n"/>
+      <c r="CF215" s="24" t="n"/>
+      <c r="CG215" s="24" t="n"/>
+      <c r="CH215" s="24" t="n"/>
+      <c r="CI215" s="24" t="n"/>
+      <c r="CJ215" s="24" t="n"/>
+      <c r="CK215" s="24" t="n"/>
+      <c r="CL215" s="24" t="n"/>
+      <c r="CM215" s="24" t="n"/>
+      <c r="CN215" s="24" t="n"/>
+      <c r="CO215" s="24" t="n"/>
+      <c r="CP215" s="24" t="n"/>
+      <c r="CQ215" s="24" t="n"/>
+      <c r="CR215" s="24" t="n"/>
+      <c r="CS215" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT215" s="24" t="n"/>
+      <c r="CU215" s="24" t="n"/>
+      <c r="CV215" s="24" t="n"/>
+      <c r="CW215" s="24" t="n"/>
+      <c r="CX215" s="24" t="n"/>
+      <c r="CY215" s="24" t="n"/>
+      <c r="CZ215" s="24" t="n"/>
+      <c r="DA215" s="24" t="n"/>
+      <c r="DB215" s="24" t="n"/>
+      <c r="DC215" s="24" t="n"/>
+      <c r="DD215" s="24" t="n"/>
+      <c r="DE215" s="24" t="n"/>
+      <c r="DF215" s="24" t="n"/>
+      <c r="DG215" s="24" t="n"/>
+      <c r="DH215" s="24" t="n"/>
+      <c r="DI215" s="24" t="n"/>
+      <c r="DJ215" s="24" t="n"/>
+      <c r="DK215" s="24" t="n"/>
+      <c r="DL215" s="24" t="n"/>
+      <c r="DM215" s="24" t="n"/>
+      <c r="DN215" s="24" t="n"/>
+      <c r="DO215" s="24" t="n"/>
+      <c r="DP215" s="24" t="n"/>
+      <c r="DQ215" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7", "away_team": "Nippon Ham Fighters", "draw_settlement_value": 0.5, "event_id": "156784", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1560.298182, "base_tie_rate": 0.02386015, "home_advantage": 35.0, "home_elo": 1619.092388}, "historical_source_observation_times_verified": false, "home_team": "Fukuoka SoftBank Hawks", "inference_inputs": {"away_id": "F", "base_tie_rate": 0.02386015, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"F": 1560.298182, "H": 1619.092388}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "H", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-13T22:28:51.412639+00:00", "outcome_probabilities": {"away": 0.3594200900286334, "draw": 0.02386015, "home": 0.6167197599713666}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.37135, "home": 0.62865}, "snapshot_hash": "dc01d7b908dd35df8593618b3851718dbff44ad9bd138f6956a263f5cf17eb97", "sport": "NPB"}</t>
         </is>
       </c>
     </row>

--- a/data/sports/npb/research.xlsx
+++ b/data/sports/npb/research.xlsx
@@ -68744,12 +68744,12 @@
     <row r="214" ht="36" customHeight="1">
       <c r="A214" s="24" t="inlineStr">
         <is>
-          <t>4d9e53576bd2462b</t>
+          <t>e1c95a5f914b4c7c</t>
         </is>
       </c>
       <c r="B214" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:28:52.203222Z</t>
+          <t>2026-10-14T05:52:01.251682Z</t>
         </is>
       </c>
       <c r="C214" s="24" t="inlineStr">
@@ -68794,20 +68794,20 @@
         </is>
       </c>
       <c r="L214" s="26" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="M214" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.641026</v>
       </c>
       <c r="N214" s="28" t="n">
-        <v>0.6</v>
+        <v>0.609375</v>
       </c>
       <c r="O214" s="28" t="n">
         <v>0.547141</v>
       </c>
       <c r="P214" s="28" t="n"/>
       <c r="Q214" s="28" t="n">
-        <v>-0.052859</v>
+        <v>-0.062234</v>
       </c>
       <c r="R214" s="26" t="n">
         <v>0</v>
@@ -68836,7 +68836,7 @@
       <c r="AD214" s="24" t="n"/>
       <c r="AE214" s="31" t="inlineStr">
         <is>
-          <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-npb-hta-ybo-2026-10-14). Tie probability=0.0239.</t>
+          <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-hta-ybo-2026-10-14). Tie probability=0.0239.</t>
         </is>
       </c>
       <c r="AF214" s="31" t="inlineStr">
@@ -68920,7 +68920,7 @@
       </c>
       <c r="BA214" s="24" t="inlineStr">
         <is>
-          <t>22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7</t>
+          <t>7fafc82f9fdb1d095962ad6674aded3d12f0af8cc89088ba34fd259b2b58c3d6</t>
         </is>
       </c>
       <c r="BB214" s="24" t="inlineStr">
@@ -68935,7 +68935,7 @@
       </c>
       <c r="BD214" s="24" t="inlineStr">
         <is>
-          <t>22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7</t>
+          <t>7fafc82f9fdb1d095962ad6674aded3d12f0af8cc89088ba34fd259b2b58c3d6</t>
         </is>
       </c>
       <c r="BE214" s="24" t="inlineStr">
@@ -68955,7 +68955,7 @@
       </c>
       <c r="BH214" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:28:51.878028Z</t>
+          <t>2026-10-14T05:52:00.939109Z</t>
         </is>
       </c>
       <c r="BI214" s="24" t="inlineStr">
@@ -68965,13 +68965,13 @@
       </c>
       <c r="BJ214" s="25" t="n"/>
       <c r="BK214" s="26" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="BL214" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.641026</v>
       </c>
       <c r="BM214" s="28" t="n">
-        <v>0.6</v>
+        <v>0.609375</v>
       </c>
       <c r="BN214" s="28" t="n"/>
       <c r="BO214" s="28" t="n"/>
@@ -69034,19 +69034,19 @@
       <c r="DP214" s="24" t="n"/>
       <c r="DQ214" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7", "away_team": "Yokohama BayStars", "draw_settlement_value": 0.5, "event_id": "154783", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1521.060932, "base_tie_rate": 0.02386015, "home_advantage": 35.0, "home_elo": 1519.723482}, "historical_source_observation_times_verified": false, "home_team": "Hanshin Tigers", "inference_inputs": {"away_id": "DB", "base_tie_rate": 0.02386015, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"DB": 1521.060932, "T": 1519.723482}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "T", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-13T22:28:51.412639+00:00", "outcome_probabilities": {"away": 0.4409289279790772, "draw": 0.02386015, "home": 0.5352109220209229}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.452859, "home": 0.547141}, "snapshot_hash": "7015e4880439a4d4afc64cf919c0221dc4d3470b546c8957dd94de8d2f5525ec", "sport": "NPB"}</t>
+          <t>{"artifact_hash": "7fafc82f9fdb1d095962ad6674aded3d12f0af8cc89088ba34fd259b2b58c3d6", "away_team": "Yokohama BayStars", "draw_settlement_value": 0.5, "event_id": "154783", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1521.060932, "base_tie_rate": 0.02386015, "home_advantage": 35.0, "home_elo": 1519.723482}, "historical_source_observation_times_verified": false, "home_team": "Hanshin Tigers", "inference_inputs": {"away_id": "DB", "base_tie_rate": 0.02386015, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"DB": 1521.060932, "T": 1519.723482}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "8d592e32eff91d945b870d7032edca3806863cff9428edece9f38d56cc36b070"}, "home_id": "T", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-14T05:52:00.228547+00:00", "outcome_probabilities": {"away": 0.4409289279790772, "draw": 0.02386015, "home": 0.5352109220209229}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.452859, "home": 0.547141}, "snapshot_hash": "b30406ee8db9b04dc143ff245b6267004e6131827375291eabdbdb240cef7142", "sport": "NPB"}</t>
         </is>
       </c>
     </row>
     <row r="215" ht="36" customHeight="1">
       <c r="A215" s="24" t="inlineStr">
         <is>
-          <t>7d0a7073fe6d4e19</t>
+          <t>6480fde6a7f745b2</t>
         </is>
       </c>
       <c r="B215" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:28:52.203222Z</t>
+          <t>2026-10-14T05:52:01.251682Z</t>
         </is>
       </c>
       <c r="C215" s="24" t="inlineStr">
@@ -69091,20 +69091,20 @@
         </is>
       </c>
       <c r="L215" s="26" t="n">
-        <v>-270</v>
+        <v>-317</v>
       </c>
       <c r="M215" s="27" t="n">
-        <v>1.37037</v>
+        <v>1.315457</v>
       </c>
       <c r="N215" s="28" t="n">
-        <v>0.72973</v>
+        <v>0.760192</v>
       </c>
       <c r="O215" s="28" t="n">
         <v>0.62865</v>
       </c>
       <c r="P215" s="28" t="n"/>
       <c r="Q215" s="28" t="n">
-        <v>-0.10108</v>
+        <v>-0.131542</v>
       </c>
       <c r="R215" s="26" t="n">
         <v>0</v>
@@ -69133,7 +69133,7 @@
       <c r="AD215" s="24" t="n"/>
       <c r="AE215" s="31" t="inlineStr">
         <is>
-          <t>Tie-aware Elo baseline; executable ask 0.7300 (market_slug=aec-npb-fsh-nhf-2026-10-14). Tie probability=0.0239.</t>
+          <t>Tie-aware Elo baseline; executable ask 0.7600 (market_slug=aec-npb-fsh-nhf-2026-10-14). Tie probability=0.0239.</t>
         </is>
       </c>
       <c r="AF215" s="31" t="inlineStr">
@@ -69217,7 +69217,7 @@
       </c>
       <c r="BA215" s="24" t="inlineStr">
         <is>
-          <t>22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7</t>
+          <t>7fafc82f9fdb1d095962ad6674aded3d12f0af8cc89088ba34fd259b2b58c3d6</t>
         </is>
       </c>
       <c r="BB215" s="24" t="inlineStr">
@@ -69232,7 +69232,7 @@
       </c>
       <c r="BD215" s="24" t="inlineStr">
         <is>
-          <t>22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7</t>
+          <t>7fafc82f9fdb1d095962ad6674aded3d12f0af8cc89088ba34fd259b2b58c3d6</t>
         </is>
       </c>
       <c r="BE215" s="24" t="inlineStr">
@@ -69252,7 +69252,7 @@
       </c>
       <c r="BH215" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:28:52.203222Z</t>
+          <t>2026-10-14T05:52:01.251682Z</t>
         </is>
       </c>
       <c r="BI215" s="24" t="inlineStr">
@@ -69262,13 +69262,13 @@
       </c>
       <c r="BJ215" s="25" t="n"/>
       <c r="BK215" s="26" t="n">
-        <v>-270</v>
+        <v>-317</v>
       </c>
       <c r="BL215" s="27" t="n">
-        <v>1.37037</v>
+        <v>1.315457</v>
       </c>
       <c r="BM215" s="28" t="n">
-        <v>0.72973</v>
+        <v>0.760192</v>
       </c>
       <c r="BN215" s="28" t="n"/>
       <c r="BO215" s="28" t="n"/>
@@ -69331,7 +69331,7 @@
       <c r="DP215" s="24" t="n"/>
       <c r="DQ215" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7", "away_team": "Nippon Ham Fighters", "draw_settlement_value": 0.5, "event_id": "156784", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1560.298182, "base_tie_rate": 0.02386015, "home_advantage": 35.0, "home_elo": 1619.092388}, "historical_source_observation_times_verified": false, "home_team": "Fukuoka SoftBank Hawks", "inference_inputs": {"away_id": "F", "base_tie_rate": 0.02386015, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"F": 1560.298182, "H": 1619.092388}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "H", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-13T22:28:51.412639+00:00", "outcome_probabilities": {"away": 0.3594200900286334, "draw": 0.02386015, "home": 0.6167197599713666}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.37135, "home": 0.62865}, "snapshot_hash": "dc01d7b908dd35df8593618b3851718dbff44ad9bd138f6956a263f5cf17eb97", "sport": "NPB"}</t>
+          <t>{"artifact_hash": "7fafc82f9fdb1d095962ad6674aded3d12f0af8cc89088ba34fd259b2b58c3d6", "away_team": "Nippon Ham Fighters", "draw_settlement_value": 0.5, "event_id": "156784", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1560.298182, "base_tie_rate": 0.02386015, "home_advantage": 35.0, "home_elo": 1619.092388}, "historical_source_observation_times_verified": false, "home_team": "Fukuoka SoftBank Hawks", "inference_inputs": {"away_id": "F", "base_tie_rate": 0.02386015, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"F": 1560.298182, "H": 1619.092388}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "8d592e32eff91d945b870d7032edca3806863cff9428edece9f38d56cc36b070"}, "home_id": "H", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-14T05:52:00.228547+00:00", "outcome_probabilities": {"away": 0.3594200900286334, "draw": 0.02386015, "home": 0.6167197599713666}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.37135, "home": 0.62865}, "snapshot_hash": "7fb05bafaa59e8a12436558c3a0f6e4e36da1e7e98aed046bbfd1840373a0929", "sport": "NPB"}</t>
         </is>
       </c>
     </row>

--- a/data/sports/npb/research.xlsx
+++ b/data/sports/npb/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ215" headerRowCount="1">
-  <autoFilter ref="A1:DQ215"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ217" headerRowCount="1">
+  <autoFilter ref="A1:DQ217"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$215)</f>
+        <f>COUNTA('Picks'!$A$2:$A$217)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$215,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$217,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$215,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$217,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"win")+COUNTIFS('Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$217,"settled",'Picks'!$V$2:$V$217,"win")+COUNTIFS('Picks'!$U$2:$U$217,"settled",'Picks'!$V$2:$V$217,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$215,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$217,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$217,"&gt;0",'Picks'!$V$2:$V$217,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$217,"&gt;0",'Picks'!$V$2:$V$217,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"win")/(COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"win")+COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$217,"&gt;0",'Picks'!$V$2:$V$217,"win")/(COUNTIFS('Picks'!$BX$2:$BX$217,"&gt;0",'Picks'!$V$2:$V$217,"win")+COUNTIFS('Picks'!$BX$2:$BX$217,"&gt;0",'Picks'!$V$2:$V$217,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$215)/SUM('Picks'!$BX$2:$BX$215),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$217)/SUM('Picks'!$BX$2:$BX$217),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$215)</f>
+        <f>SUM('Picks'!$BY$2:$BY$217)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$215,"&lt;&gt;",'Picks'!$AB$2:$AB$215),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$217,"&lt;&gt;",'Picks'!$AB$2:$AB$217),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$215,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$215,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$217,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$217,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$215,'Picks'!$AM$2:$AM$215,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$217,'Picks'!$AM$2:$AM$217,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A14,'Picks'!$U$2:$U$215,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A14,'Picks'!$U$2:$U$217,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A14,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A14,'Picks'!$U$2:$U$217,"settled",'Picks'!$V$2:$V$217,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A14,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A14,'Picks'!$U$2:$U$217,"settled",'Picks'!$V$2:$V$217,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$215,'Picks'!$H$2:$H$215,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$217,'Picks'!$H$2:$H$217,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$215,'Picks'!$H$2:$H$215,$A14,'Picks'!$U$2:$U$215,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$217,'Picks'!$H$2:$H$217,$A14,'Picks'!$U$2:$U$217,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A15,'Picks'!$U$2:$U$215,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A15,'Picks'!$U$2:$U$217,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A15,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A15,'Picks'!$U$2:$U$217,"settled",'Picks'!$V$2:$V$217,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A15,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A15,'Picks'!$U$2:$U$217,"settled",'Picks'!$V$2:$V$217,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$215,'Picks'!$H$2:$H$215,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$217,'Picks'!$H$2:$H$217,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$215,'Picks'!$H$2:$H$215,$A15,'Picks'!$U$2:$U$215,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$217,'Picks'!$H$2:$H$217,$A15,'Picks'!$U$2:$U$217,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A16,'Picks'!$U$2:$U$215,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A16,'Picks'!$U$2:$U$217,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A16,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A16,'Picks'!$U$2:$U$217,"settled",'Picks'!$V$2:$V$217,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A16,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A16,'Picks'!$U$2:$U$217,"settled",'Picks'!$V$2:$V$217,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$215,'Picks'!$H$2:$H$215,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$217,'Picks'!$H$2:$H$217,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$215,'Picks'!$H$2:$H$215,$A16,'Picks'!$U$2:$U$215,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$217,'Picks'!$H$2:$H$217,$A16,'Picks'!$U$2:$U$217,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ215"/>
+  <dimension ref="A1:DQ217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -68822,18 +68822,38 @@
       </c>
       <c r="U214" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V214" s="24" t="n"/>
-      <c r="W214" s="26" t="n"/>
-      <c r="X214" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V214" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W214" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X214" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y214" s="25" t="n"/>
-      <c r="Z214" s="26" t="n"/>
-      <c r="AA214" s="28" t="n"/>
-      <c r="AB214" s="28" t="n"/>
-      <c r="AC214" s="30" t="n"/>
-      <c r="AD214" s="24" t="n"/>
+      <c r="Z214" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="AA214" s="28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB214" s="28" t="n">
+        <v>0.000625</v>
+      </c>
+      <c r="AC214" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD214" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:03:59.496089Z</t>
+        </is>
+      </c>
       <c r="AE214" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-hta-ybo-2026-10-14). Tie probability=0.0239.</t>
@@ -68846,7 +68866,7 @@
       </c>
       <c r="AG214" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH214" s="24" t="n"/>
@@ -68976,8 +68996,12 @@
       <c r="BN214" s="28" t="n"/>
       <c r="BO214" s="28" t="n"/>
       <c r="BP214" s="25" t="n"/>
-      <c r="BQ214" s="27" t="n"/>
-      <c r="BR214" s="28" t="n"/>
+      <c r="BQ214" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BR214" s="28" t="n">
+        <v>0.61</v>
+      </c>
       <c r="BS214" s="28" t="n"/>
       <c r="BT214" s="28" t="n"/>
       <c r="BU214" s="25" t="n"/>
@@ -69119,18 +69143,38 @@
       </c>
       <c r="U215" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V215" s="24" t="n"/>
-      <c r="W215" s="26" t="n"/>
-      <c r="X215" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V215" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W215" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X215" s="26" t="n">
+        <v>6</v>
+      </c>
       <c r="Y215" s="25" t="n"/>
-      <c r="Z215" s="26" t="n"/>
-      <c r="AA215" s="28" t="n"/>
-      <c r="AB215" s="28" t="n"/>
-      <c r="AC215" s="30" t="n"/>
-      <c r="AD215" s="24" t="n"/>
+      <c r="Z215" s="26" t="n">
+        <v>-317</v>
+      </c>
+      <c r="AA215" s="28" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AB215" s="28" t="n">
+        <v>-0.000192</v>
+      </c>
+      <c r="AC215" s="30" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="AD215" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:04:01.170688Z</t>
+        </is>
+      </c>
       <c r="AE215" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.7600 (market_slug=aec-npb-fsh-nhf-2026-10-14). Tie probability=0.0239.</t>
@@ -69273,8 +69317,12 @@
       <c r="BN215" s="28" t="n"/>
       <c r="BO215" s="28" t="n"/>
       <c r="BP215" s="25" t="n"/>
-      <c r="BQ215" s="27" t="n"/>
-      <c r="BR215" s="28" t="n"/>
+      <c r="BQ215" s="27" t="n">
+        <v>1.315457</v>
+      </c>
+      <c r="BR215" s="28" t="n">
+        <v>0.76</v>
+      </c>
       <c r="BS215" s="28" t="n"/>
       <c r="BT215" s="28" t="n"/>
       <c r="BU215" s="25" t="n"/>
@@ -69335,6 +69383,600 @@
         </is>
       </c>
     </row>
+    <row r="216" ht="36" customHeight="1">
+      <c r="A216" s="24" t="inlineStr">
+        <is>
+          <t>eb4f576cc8c84631</t>
+        </is>
+      </c>
+      <c r="B216" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:46:05.499523Z</t>
+        </is>
+      </c>
+      <c r="C216" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D216" s="24" t="inlineStr">
+        <is>
+          <t>156226</t>
+        </is>
+      </c>
+      <c r="E216" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F216" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="G216" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="H216" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I216" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J216" s="25" t="n"/>
+      <c r="K216" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L216" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M216" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N216" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O216" s="28" t="n">
+        <v>0.534905</v>
+      </c>
+      <c r="P216" s="28" t="n"/>
+      <c r="Q216" s="28" t="n">
+        <v>-0.124959</v>
+      </c>
+      <c r="R216" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S216" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T216" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U216" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V216" s="24" t="n"/>
+      <c r="W216" s="26" t="n"/>
+      <c r="X216" s="26" t="n"/>
+      <c r="Y216" s="25" t="n"/>
+      <c r="Z216" s="26" t="n"/>
+      <c r="AA216" s="28" t="n"/>
+      <c r="AB216" s="28" t="n"/>
+      <c r="AC216" s="30" t="n"/>
+      <c r="AD216" s="24" t="n"/>
+      <c r="AE216" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6600 (market_slug=aec-npb-hta-ybo-2026-10-15). Tie probability=0.0238.</t>
+        </is>
+      </c>
+      <c r="AF216" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG216" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH216" s="24" t="n"/>
+      <c r="AI216" s="31" t="n"/>
+      <c r="AJ216" s="31" t="n"/>
+      <c r="AK216" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL216" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM216" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN216" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO216" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP216" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AQ216" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AR216" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AS216" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AT216" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AU216" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AV216" s="24" t="n"/>
+      <c r="AW216" s="24" t="n"/>
+      <c r="AX216" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY216" s="24" t="n"/>
+      <c r="AZ216" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA216" s="24" t="inlineStr">
+        <is>
+          <t>825df62f7ca8ea80080b80e8de2f09e2cd7396038ed7b0fc994bf7724010e642</t>
+        </is>
+      </c>
+      <c r="BB216" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC216" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD216" s="24" t="inlineStr">
+        <is>
+          <t>825df62f7ca8ea80080b80e8de2f09e2cd7396038ed7b0fc994bf7724010e642</t>
+        </is>
+      </c>
+      <c r="BE216" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF216" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG216" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH216" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:46:05.438749Z</t>
+        </is>
+      </c>
+      <c r="BI216" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ216" s="25" t="n"/>
+      <c r="BK216" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL216" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM216" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN216" s="28" t="n"/>
+      <c r="BO216" s="28" t="n"/>
+      <c r="BP216" s="25" t="n"/>
+      <c r="BQ216" s="27" t="n"/>
+      <c r="BR216" s="28" t="n"/>
+      <c r="BS216" s="28" t="n"/>
+      <c r="BT216" s="28" t="n"/>
+      <c r="BU216" s="25" t="n"/>
+      <c r="BV216" s="29" t="n"/>
+      <c r="BW216" s="24" t="n"/>
+      <c r="BX216" s="30" t="n"/>
+      <c r="BY216" s="27" t="n"/>
+      <c r="BZ216" s="24" t="n"/>
+      <c r="CA216" s="31" t="n"/>
+      <c r="CB216" s="24" t="n"/>
+      <c r="CC216" s="24" t="n"/>
+      <c r="CD216" s="24" t="n"/>
+      <c r="CE216" s="24" t="n"/>
+      <c r="CF216" s="24" t="n"/>
+      <c r="CG216" s="24" t="n"/>
+      <c r="CH216" s="24" t="n"/>
+      <c r="CI216" s="24" t="n"/>
+      <c r="CJ216" s="24" t="n"/>
+      <c r="CK216" s="24" t="n"/>
+      <c r="CL216" s="24" t="n"/>
+      <c r="CM216" s="24" t="n"/>
+      <c r="CN216" s="24" t="n"/>
+      <c r="CO216" s="24" t="n"/>
+      <c r="CP216" s="24" t="n"/>
+      <c r="CQ216" s="24" t="n"/>
+      <c r="CR216" s="24" t="n"/>
+      <c r="CS216" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT216" s="24" t="n"/>
+      <c r="CU216" s="24" t="n"/>
+      <c r="CV216" s="24" t="n"/>
+      <c r="CW216" s="24" t="n"/>
+      <c r="CX216" s="24" t="n"/>
+      <c r="CY216" s="24" t="n"/>
+      <c r="CZ216" s="24" t="n"/>
+      <c r="DA216" s="24" t="n"/>
+      <c r="DB216" s="24" t="n"/>
+      <c r="DC216" s="24" t="n"/>
+      <c r="DD216" s="24" t="n"/>
+      <c r="DE216" s="24" t="n"/>
+      <c r="DF216" s="24" t="n"/>
+      <c r="DG216" s="24" t="n"/>
+      <c r="DH216" s="24" t="n"/>
+      <c r="DI216" s="24" t="n"/>
+      <c r="DJ216" s="24" t="n"/>
+      <c r="DK216" s="24" t="n"/>
+      <c r="DL216" s="24" t="n"/>
+      <c r="DM216" s="24" t="n"/>
+      <c r="DN216" s="24" t="n"/>
+      <c r="DO216" s="24" t="n"/>
+      <c r="DP216" s="24" t="n"/>
+      <c r="DQ216" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "825df62f7ca8ea80080b80e8de2f09e2cd7396038ed7b0fc994bf7724010e642", "away_team": "Yokohama BayStars", "draw_settlement_value": 0.5, "event_id": "156226", "event_start_utc": "2026-10-15T09:00:00Z", "features": {"away_elo": 1525.447278, "base_tie_rate": 0.02384888, "home_advantage": 35.0, "home_elo": 1515.337136}, "historical_source_observation_times_verified": false, "home_team": "Hanshin Tigers", "inference_inputs": {"away_id": "DB", "base_tie_rate": 0.02384888, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"DB": 1525.447278, "T": 1515.337136}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "8d592e32eff91d945b870d7032edca3806863cff9428edece9f38d56cc36b070"}, "home_id": "T", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-14T22:46:05.368217+00:00", "outcome_probabilities": {"away": 0.4531701196880638, "draw": 0.02384888, "home": 0.5229810003119363}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.465095, "home": 0.534905}, "snapshot_hash": "acf6820d40f58e4ca0f96699fe2d4db9c3d95828363255af30a1d7db203fb88e", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="36" customHeight="1">
+      <c r="A217" s="24" t="inlineStr">
+        <is>
+          <t>c7ddfa77fa1e443a</t>
+        </is>
+      </c>
+      <c r="B217" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:46:05.499523Z</t>
+        </is>
+      </c>
+      <c r="C217" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D217" s="24" t="inlineStr">
+        <is>
+          <t>156785</t>
+        </is>
+      </c>
+      <c r="E217" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F217" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="G217" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="H217" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I217" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J217" s="25" t="n"/>
+      <c r="K217" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L217" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M217" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N217" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O217" s="28" t="n">
+        <v>0.636317</v>
+      </c>
+      <c r="P217" s="28" t="n"/>
+      <c r="Q217" s="28" t="n">
+        <v>0.016545</v>
+      </c>
+      <c r="R217" s="26" t="n">
+        <v>28</v>
+      </c>
+      <c r="S217" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T217" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U217" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V217" s="24" t="n"/>
+      <c r="W217" s="26" t="n"/>
+      <c r="X217" s="26" t="n"/>
+      <c r="Y217" s="25" t="n"/>
+      <c r="Z217" s="26" t="n"/>
+      <c r="AA217" s="28" t="n"/>
+      <c r="AB217" s="28" t="n"/>
+      <c r="AC217" s="30" t="n"/>
+      <c r="AD217" s="24" t="n"/>
+      <c r="AE217" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6200 (market_slug=aec-npb-fsh-nhf-2026-10-15). Tie probability=0.0238.</t>
+        </is>
+      </c>
+      <c r="AF217" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG217" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH217" s="24" t="n"/>
+      <c r="AI217" s="31" t="n"/>
+      <c r="AJ217" s="31" t="n"/>
+      <c r="AK217" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL217" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM217" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN217" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO217" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP217" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AQ217" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AR217" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AS217" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AT217" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AU217" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AV217" s="24" t="n"/>
+      <c r="AW217" s="24" t="n"/>
+      <c r="AX217" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY217" s="24" t="n"/>
+      <c r="AZ217" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA217" s="24" t="inlineStr">
+        <is>
+          <t>825df62f7ca8ea80080b80e8de2f09e2cd7396038ed7b0fc994bf7724010e642</t>
+        </is>
+      </c>
+      <c r="BB217" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC217" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD217" s="24" t="inlineStr">
+        <is>
+          <t>825df62f7ca8ea80080b80e8de2f09e2cd7396038ed7b0fc994bf7724010e642</t>
+        </is>
+      </c>
+      <c r="BE217" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF217" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG217" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH217" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:46:05.499523Z</t>
+        </is>
+      </c>
+      <c r="BI217" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ217" s="25" t="n"/>
+      <c r="BK217" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL217" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM217" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN217" s="28" t="n"/>
+      <c r="BO217" s="28" t="n"/>
+      <c r="BP217" s="25" t="n"/>
+      <c r="BQ217" s="27" t="n"/>
+      <c r="BR217" s="28" t="n"/>
+      <c r="BS217" s="28" t="n"/>
+      <c r="BT217" s="28" t="n"/>
+      <c r="BU217" s="25" t="n"/>
+      <c r="BV217" s="29" t="n"/>
+      <c r="BW217" s="24" t="n"/>
+      <c r="BX217" s="30" t="n"/>
+      <c r="BY217" s="27" t="n"/>
+      <c r="BZ217" s="24" t="n"/>
+      <c r="CA217" s="31" t="n"/>
+      <c r="CB217" s="24" t="n"/>
+      <c r="CC217" s="24" t="n"/>
+      <c r="CD217" s="24" t="n"/>
+      <c r="CE217" s="24" t="n"/>
+      <c r="CF217" s="24" t="n"/>
+      <c r="CG217" s="24" t="n"/>
+      <c r="CH217" s="24" t="n"/>
+      <c r="CI217" s="24" t="n"/>
+      <c r="CJ217" s="24" t="n"/>
+      <c r="CK217" s="24" t="n"/>
+      <c r="CL217" s="24" t="n"/>
+      <c r="CM217" s="24" t="n"/>
+      <c r="CN217" s="24" t="n"/>
+      <c r="CO217" s="24" t="n"/>
+      <c r="CP217" s="24" t="n"/>
+      <c r="CQ217" s="24" t="n"/>
+      <c r="CR217" s="24" t="n"/>
+      <c r="CS217" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT217" s="24" t="n"/>
+      <c r="CU217" s="24" t="n"/>
+      <c r="CV217" s="24" t="n"/>
+      <c r="CW217" s="24" t="n"/>
+      <c r="CX217" s="24" t="n"/>
+      <c r="CY217" s="24" t="n"/>
+      <c r="CZ217" s="24" t="n"/>
+      <c r="DA217" s="24" t="n"/>
+      <c r="DB217" s="24" t="n"/>
+      <c r="DC217" s="24" t="n"/>
+      <c r="DD217" s="24" t="n"/>
+      <c r="DE217" s="24" t="n"/>
+      <c r="DF217" s="24" t="n"/>
+      <c r="DG217" s="24" t="n"/>
+      <c r="DH217" s="24" t="n"/>
+      <c r="DI217" s="24" t="n"/>
+      <c r="DJ217" s="24" t="n"/>
+      <c r="DK217" s="24" t="n"/>
+      <c r="DL217" s="24" t="n"/>
+      <c r="DM217" s="24" t="n"/>
+      <c r="DN217" s="24" t="n"/>
+      <c r="DO217" s="24" t="n"/>
+      <c r="DP217" s="24" t="n"/>
+      <c r="DQ217" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "825df62f7ca8ea80080b80e8de2f09e2cd7396038ed7b0fc994bf7724010e642", "away_team": "Nippon Ham Fighters", "draw_settlement_value": 0.5, "event_id": "156785", "event_start_utc": "2026-10-15T09:00:00Z", "features": {"away_elo": 1557.352538, "base_tie_rate": 0.02384888, "home_advantage": 35.0, "home_elo": 1622.038032}, "historical_source_observation_times_verified": false, "home_team": "Fukuoka SoftBank Hawks", "inference_inputs": {"away_id": "F", "base_tie_rate": 0.02384888, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"F": 1557.352538, "H": 1622.038032}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "8d592e32eff91d945b870d7032edca3806863cff9428edece9f38d56cc36b070"}, "home_id": "H", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-14T22:46:05.368217+00:00", "outcome_probabilities": {"away": 0.35175820242487227, "draw": 0.02384888, "home": 0.6243929175751278}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.363683, "home": 0.636317}, "snapshot_hash": "2466aa23573c156d1651fe119740c418f306c08e4cbdcd51b46301025ecbf80b", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
